--- a/frontend/test_data/header_detection/Large_Valid_Standard_Test.xlsx
+++ b/frontend/test_data/header_detection/Large_Valid_Standard_Test.xlsx
@@ -4606,7 +4606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4616,37 +4616,40 @@
         <v>Row Preview</v>
       </c>
       <c r="C1" t="str">
-        <v>Density Bonus</v>
+        <v>Pillar 1: Density (%)</v>
       </c>
       <c r="D1" t="str">
-        <v>Data Boundary Signal</v>
+        <v>Pillar 2: Boundary (%)</v>
       </c>
       <c r="E1" t="str">
-        <v>Consistent String Signal</v>
+        <v>Pillar 3: Consistency (%)</v>
       </c>
       <c r="F1" t="str">
-        <v>Consistent Numeric Signal</v>
+        <v>Pillar 4: Traits (%)</v>
       </c>
       <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
       <c r="H1" t="str">
-        <v>Numeric Data Penalty</v>
+        <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Pivoted Series Bonus</v>
+        <v>Search Booster (Pivoted)</v>
       </c>
       <c r="J1" t="str">
-        <v>100% String Bonus</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Unique Values Rule</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="L1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL SCORE</v>
+        <v>TOTAL RAW SCORE</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
     <row r="2">
@@ -4657,16 +4660,16 @@
         <v>["SMARTBRIDGE DENSE STANDARD REPORT"]</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -4678,16 +4681,19 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="N2">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -4698,16 +4704,16 @@
         <v>["Export Date: 2026-06-16"]</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -4719,16 +4725,19 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="N3">
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -4739,16 +4748,16 @@
         <v>["Author: QA Automation Engine"]</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -4760,16 +4769,19 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>17</v>
+        <v>49</v>
+      </c>
+      <c r="N4">
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -4780,17 +4792,17 @@
         <v>["Vendor ID","Company Name","Contact Email","Invoi</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
         <v>15</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -4801,16 +4813,19 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>70</v>
+        <v>96</v>
+      </c>
+      <c r="N5">
+        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -4821,22 +4836,22 @@
         <v>["SUP-1000","Acme Logistics Solutions 0 LLC","cont</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4845,13 +4860,16 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N6">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -4862,22 +4880,22 @@
         <v>["SUP-1001","Acme Logistics Solutions 1 LLC","cont</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4886,13 +4904,16 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N7">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -4903,22 +4924,22 @@
         <v>["SUP-1002","Acme Logistics Solutions 2 LLC","cont</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4927,13 +4948,16 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N8">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -4944,22 +4968,22 @@
         <v>["SUP-1003","Acme Logistics Solutions 3 LLC","cont</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4968,13 +4992,16 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N9">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -4985,22 +5012,22 @@
         <v>["SUP-1004","Acme Logistics Solutions 4 LLC","cont</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -5009,13 +5036,16 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N10">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -5026,22 +5056,22 @@
         <v>["SUP-1005","Acme Logistics Solutions 5 LLC","cont</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -5050,13 +5080,16 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N11">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -5067,22 +5100,22 @@
         <v>["SUP-1006","Acme Logistics Solutions 6 LLC","cont</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -5091,13 +5124,16 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N12">
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -5108,22 +5144,22 @@
         <v>["SUP-1007","Acme Logistics Solutions 7 LLC","cont</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -5132,13 +5168,16 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N13">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -5149,22 +5188,22 @@
         <v>["SUP-1008","Acme Logistics Solutions 8 LLC","cont</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -5173,13 +5212,16 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N14">
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -5190,22 +5232,22 @@
         <v>["SUP-1009","Acme Logistics Solutions 9 LLC","cont</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -5214,13 +5256,16 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N15">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -5231,22 +5276,22 @@
         <v>["SUP-1010","Acme Logistics Solutions 10 LLC","con</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5255,13 +5300,16 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N16">
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -5272,22 +5320,22 @@
         <v>["SUP-1011","Acme Logistics Solutions 11 LLC","con</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5296,13 +5344,16 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N17">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -5313,22 +5364,22 @@
         <v>["SUP-1012","Acme Logistics Solutions 12 LLC","con</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5337,13 +5388,16 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N18">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -5354,22 +5408,22 @@
         <v>["SUP-1013","Acme Logistics Solutions 13 LLC","con</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -5378,13 +5432,16 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N19">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -5395,22 +5452,22 @@
         <v>["SUP-1014","Acme Logistics Solutions 14 LLC","con</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5419,18 +5476,7941 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="N20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>["SUP-1015","Acme Logistics Solutions 15 LLC","con</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>21</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>-30</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>16</v>
+      </c>
+      <c r="N21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>["SUP-1016","Acme Logistics Solutions 16 LLC","con</v>
+      </c>
+      <c r="C22">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>21</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>-30</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+      <c r="M22">
+        <v>16</v>
+      </c>
+      <c r="N22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>["SUP-1017","Acme Logistics Solutions 17 LLC","con</v>
+      </c>
+      <c r="C23">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>21</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>-30</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+      <c r="M23">
+        <v>16</v>
+      </c>
+      <c r="N23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>["SUP-1018","Acme Logistics Solutions 18 LLC","con</v>
+      </c>
+      <c r="C24">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>21</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>-30</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>5</v>
+      </c>
+      <c r="M24">
+        <v>16</v>
+      </c>
+      <c r="N24">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>["SUP-1019","Acme Logistics Solutions 19 LLC","con</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>21</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>-30</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
+      </c>
+      <c r="M25">
+        <v>16</v>
+      </c>
+      <c r="N25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>["SUP-1020","Acme Logistics Solutions 20 LLC","con</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>21</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>-30</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
+      </c>
+      <c r="M26">
+        <v>16</v>
+      </c>
+      <c r="N26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>["SUP-1021","Acme Logistics Solutions 21 LLC","con</v>
+      </c>
+      <c r="C27">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>21</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>-30</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>16</v>
+      </c>
+      <c r="N27">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>["SUP-1022","Acme Logistics Solutions 22 LLC","con</v>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>21</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>-30</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>5</v>
+      </c>
+      <c r="M28">
+        <v>16</v>
+      </c>
+      <c r="N28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>["SUP-1023","Acme Logistics Solutions 23 LLC","con</v>
+      </c>
+      <c r="C29">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>21</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>-30</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
+      <c r="M29">
+        <v>16</v>
+      </c>
+      <c r="N29">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="str">
+        <v>["SUP-1024","Acme Logistics Solutions 24 LLC","con</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>21</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>-30</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+      <c r="M30">
+        <v>16</v>
+      </c>
+      <c r="N30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="str">
+        <v>["SUP-1025","Acme Logistics Solutions 25 LLC","con</v>
+      </c>
+      <c r="C31">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>21</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>-30</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>5</v>
+      </c>
+      <c r="M31">
+        <v>16</v>
+      </c>
+      <c r="N31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>32</v>
+      </c>
+      <c r="B32" t="str">
+        <v>["SUP-1026","Acme Logistics Solutions 26 LLC","con</v>
+      </c>
+      <c r="C32">
+        <v>20</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>21</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>-30</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>5</v>
+      </c>
+      <c r="M32">
+        <v>16</v>
+      </c>
+      <c r="N32">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>33</v>
+      </c>
+      <c r="B33" t="str">
+        <v>["SUP-1027","Acme Logistics Solutions 27 LLC","con</v>
+      </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>21</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>-30</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>5</v>
+      </c>
+      <c r="M33">
+        <v>16</v>
+      </c>
+      <c r="N33">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="str">
+        <v>["SUP-1028","Acme Logistics Solutions 28 LLC","con</v>
+      </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>21</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>-30</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>5</v>
+      </c>
+      <c r="M34">
+        <v>16</v>
+      </c>
+      <c r="N34">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="str">
+        <v>["SUP-1029","Acme Logistics Solutions 29 LLC","con</v>
+      </c>
+      <c r="C35">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>21</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>-30</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>5</v>
+      </c>
+      <c r="M35">
+        <v>16</v>
+      </c>
+      <c r="N35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="str">
+        <v>["SUP-1030","Acme Logistics Solutions 30 LLC","con</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>21</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>-30</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
+      </c>
+      <c r="M36">
+        <v>16</v>
+      </c>
+      <c r="N36">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="str">
+        <v>["SUP-1031","Acme Logistics Solutions 31 LLC","con</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>21</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>-30</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+      <c r="M37">
+        <v>16</v>
+      </c>
+      <c r="N37">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="str">
+        <v>["SUP-1032","Acme Logistics Solutions 32 LLC","con</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>21</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>-30</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>5</v>
+      </c>
+      <c r="M38">
+        <v>16</v>
+      </c>
+      <c r="N38">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="str">
+        <v>["SUP-1033","Acme Logistics Solutions 33 LLC","con</v>
+      </c>
+      <c r="C39">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>21</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>-30</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>5</v>
+      </c>
+      <c r="M39">
+        <v>16</v>
+      </c>
+      <c r="N39">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="str">
+        <v>["SUP-1034","Acme Logistics Solutions 34 LLC","con</v>
+      </c>
+      <c r="C40">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>21</v>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>-30</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>5</v>
+      </c>
+      <c r="M40">
+        <v>16</v>
+      </c>
+      <c r="N40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="str">
+        <v>["SUP-1035","Acme Logistics Solutions 35 LLC","con</v>
+      </c>
+      <c r="C41">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>21</v>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>-30</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>5</v>
+      </c>
+      <c r="M41">
+        <v>16</v>
+      </c>
+      <c r="N41">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42" t="str">
+        <v>["SUP-1036","Acme Logistics Solutions 36 LLC","con</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>21</v>
+      </c>
+      <c r="F42">
+        <v>5</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>-30</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>16</v>
+      </c>
+      <c r="N42">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43" t="str">
+        <v>["SUP-1037","Acme Logistics Solutions 37 LLC","con</v>
+      </c>
+      <c r="C43">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>21</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>-30</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>5</v>
+      </c>
+      <c r="M43">
+        <v>16</v>
+      </c>
+      <c r="N43">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>44</v>
+      </c>
+      <c r="B44" t="str">
+        <v>["SUP-1038","Acme Logistics Solutions 38 LLC","con</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>21</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>-30</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>5</v>
+      </c>
+      <c r="M44">
+        <v>16</v>
+      </c>
+      <c r="N44">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>45</v>
+      </c>
+      <c r="B45" t="str">
+        <v>["SUP-1039","Acme Logistics Solutions 39 LLC","con</v>
+      </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>21</v>
+      </c>
+      <c r="F45">
+        <v>5</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>-30</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>5</v>
+      </c>
+      <c r="M45">
+        <v>16</v>
+      </c>
+      <c r="N45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46" t="str">
+        <v>["SUP-1040","Acme Logistics Solutions 40 LLC","con</v>
+      </c>
+      <c r="C46">
+        <v>20</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>21</v>
+      </c>
+      <c r="F46">
+        <v>5</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>-30</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>5</v>
+      </c>
+      <c r="M46">
+        <v>16</v>
+      </c>
+      <c r="N46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>47</v>
+      </c>
+      <c r="B47" t="str">
+        <v>["SUP-1041","Acme Logistics Solutions 41 LLC","con</v>
+      </c>
+      <c r="C47">
+        <v>20</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>21</v>
+      </c>
+      <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>-30</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>5</v>
+      </c>
+      <c r="M47">
+        <v>16</v>
+      </c>
+      <c r="N47">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>48</v>
+      </c>
+      <c r="B48" t="str">
+        <v>["SUP-1042","Acme Logistics Solutions 42 LLC","con</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>21</v>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>-30</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>5</v>
+      </c>
+      <c r="M48">
+        <v>16</v>
+      </c>
+      <c r="N48">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>49</v>
+      </c>
+      <c r="B49" t="str">
+        <v>["SUP-1043","Acme Logistics Solutions 43 LLC","con</v>
+      </c>
+      <c r="C49">
+        <v>20</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>21</v>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>-30</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>5</v>
+      </c>
+      <c r="M49">
+        <v>16</v>
+      </c>
+      <c r="N49">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" t="str">
+        <v>["SUP-1044","Acme Logistics Solutions 44 LLC","con</v>
+      </c>
+      <c r="C50">
+        <v>20</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>21</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>-30</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>5</v>
+      </c>
+      <c r="M50">
+        <v>16</v>
+      </c>
+      <c r="N50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>51</v>
+      </c>
+      <c r="B51" t="str">
+        <v>["SUP-1045","Acme Logistics Solutions 45 LLC","con</v>
+      </c>
+      <c r="C51">
+        <v>20</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>21</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>-30</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>5</v>
+      </c>
+      <c r="M51">
+        <v>16</v>
+      </c>
+      <c r="N51">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>52</v>
+      </c>
+      <c r="B52" t="str">
+        <v>["SUP-1046","Acme Logistics Solutions 46 LLC","con</v>
+      </c>
+      <c r="C52">
+        <v>20</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>21</v>
+      </c>
+      <c r="F52">
+        <v>5</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>-30</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>5</v>
+      </c>
+      <c r="M52">
+        <v>16</v>
+      </c>
+      <c r="N52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>53</v>
+      </c>
+      <c r="B53" t="str">
+        <v>["SUP-1047","Acme Logistics Solutions 47 LLC","con</v>
+      </c>
+      <c r="C53">
+        <v>20</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>21</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>-30</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>5</v>
+      </c>
+      <c r="M53">
+        <v>16</v>
+      </c>
+      <c r="N53">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" t="str">
+        <v>["SUP-1048","Acme Logistics Solutions 48 LLC","con</v>
+      </c>
+      <c r="C54">
+        <v>20</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>21</v>
+      </c>
+      <c r="F54">
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>-30</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>5</v>
+      </c>
+      <c r="M54">
+        <v>16</v>
+      </c>
+      <c r="N54">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>55</v>
+      </c>
+      <c r="B55" t="str">
+        <v>["SUP-1049","Acme Logistics Solutions 49 LLC","con</v>
+      </c>
+      <c r="C55">
+        <v>20</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>21</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>-30</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>5</v>
+      </c>
+      <c r="M55">
+        <v>16</v>
+      </c>
+      <c r="N55">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>56</v>
+      </c>
+      <c r="B56" t="str">
+        <v>["SUP-1050","Acme Logistics Solutions 50 LLC","con</v>
+      </c>
+      <c r="C56">
+        <v>20</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>21</v>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>-30</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>5</v>
+      </c>
+      <c r="M56">
+        <v>16</v>
+      </c>
+      <c r="N56">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>57</v>
+      </c>
+      <c r="B57" t="str">
+        <v>["SUP-1051","Acme Logistics Solutions 51 LLC","con</v>
+      </c>
+      <c r="C57">
+        <v>20</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>21</v>
+      </c>
+      <c r="F57">
+        <v>5</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>-30</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>5</v>
+      </c>
+      <c r="M57">
+        <v>16</v>
+      </c>
+      <c r="N57">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58" t="str">
+        <v>["SUP-1052","Acme Logistics Solutions 52 LLC","con</v>
+      </c>
+      <c r="C58">
+        <v>20</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>21</v>
+      </c>
+      <c r="F58">
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>-30</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>5</v>
+      </c>
+      <c r="M58">
+        <v>16</v>
+      </c>
+      <c r="N58">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59" t="str">
+        <v>["SUP-1053","Acme Logistics Solutions 53 LLC","con</v>
+      </c>
+      <c r="C59">
+        <v>20</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>21</v>
+      </c>
+      <c r="F59">
+        <v>5</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>-30</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>5</v>
+      </c>
+      <c r="M59">
+        <v>16</v>
+      </c>
+      <c r="N59">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>60</v>
+      </c>
+      <c r="B60" t="str">
+        <v>["SUP-1054","Acme Logistics Solutions 54 LLC","con</v>
+      </c>
+      <c r="C60">
+        <v>20</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>21</v>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>-30</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>5</v>
+      </c>
+      <c r="M60">
+        <v>16</v>
+      </c>
+      <c r="N60">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>61</v>
+      </c>
+      <c r="B61" t="str">
+        <v>["SUP-1055","Acme Logistics Solutions 55 LLC","con</v>
+      </c>
+      <c r="C61">
+        <v>20</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>21</v>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>-30</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>5</v>
+      </c>
+      <c r="M61">
+        <v>16</v>
+      </c>
+      <c r="N61">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>62</v>
+      </c>
+      <c r="B62" t="str">
+        <v>["SUP-1056","Acme Logistics Solutions 56 LLC","con</v>
+      </c>
+      <c r="C62">
+        <v>20</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>21</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>-30</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>5</v>
+      </c>
+      <c r="M62">
+        <v>16</v>
+      </c>
+      <c r="N62">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" t="str">
+        <v>["SUP-1057","Acme Logistics Solutions 57 LLC","con</v>
+      </c>
+      <c r="C63">
+        <v>20</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>21</v>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>-30</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>5</v>
+      </c>
+      <c r="M63">
+        <v>16</v>
+      </c>
+      <c r="N63">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64" t="str">
+        <v>["SUP-1058","Acme Logistics Solutions 58 LLC","con</v>
+      </c>
+      <c r="C64">
+        <v>20</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>21</v>
+      </c>
+      <c r="F64">
+        <v>5</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>-30</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>5</v>
+      </c>
+      <c r="M64">
+        <v>16</v>
+      </c>
+      <c r="N64">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65" t="str">
+        <v>["SUP-1059","Acme Logistics Solutions 59 LLC","con</v>
+      </c>
+      <c r="C65">
+        <v>20</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>21</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>-30</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>5</v>
+      </c>
+      <c r="M65">
+        <v>16</v>
+      </c>
+      <c r="N65">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>66</v>
+      </c>
+      <c r="B66" t="str">
+        <v>["SUP-1060","Acme Logistics Solutions 60 LLC","con</v>
+      </c>
+      <c r="C66">
+        <v>20</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>21</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>-30</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>5</v>
+      </c>
+      <c r="M66">
+        <v>16</v>
+      </c>
+      <c r="N66">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>67</v>
+      </c>
+      <c r="B67" t="str">
+        <v>["SUP-1061","Acme Logistics Solutions 61 LLC","con</v>
+      </c>
+      <c r="C67">
+        <v>20</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>21</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>-30</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>5</v>
+      </c>
+      <c r="M67">
+        <v>16</v>
+      </c>
+      <c r="N67">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>68</v>
+      </c>
+      <c r="B68" t="str">
+        <v>["SUP-1062","Acme Logistics Solutions 62 LLC","con</v>
+      </c>
+      <c r="C68">
+        <v>20</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>21</v>
+      </c>
+      <c r="F68">
+        <v>5</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>-30</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>5</v>
+      </c>
+      <c r="M68">
+        <v>16</v>
+      </c>
+      <c r="N68">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>69</v>
+      </c>
+      <c r="B69" t="str">
+        <v>["SUP-1063","Acme Logistics Solutions 63 LLC","con</v>
+      </c>
+      <c r="C69">
+        <v>20</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>21</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>-30</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>5</v>
+      </c>
+      <c r="M69">
+        <v>16</v>
+      </c>
+      <c r="N69">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>70</v>
+      </c>
+      <c r="B70" t="str">
+        <v>["SUP-1064","Acme Logistics Solutions 64 LLC","con</v>
+      </c>
+      <c r="C70">
+        <v>20</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>21</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>-30</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>5</v>
+      </c>
+      <c r="M70">
+        <v>16</v>
+      </c>
+      <c r="N70">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>71</v>
+      </c>
+      <c r="B71" t="str">
+        <v>["SUP-1065","Acme Logistics Solutions 65 LLC","con</v>
+      </c>
+      <c r="C71">
+        <v>20</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>21</v>
+      </c>
+      <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>-30</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>5</v>
+      </c>
+      <c r="M71">
+        <v>16</v>
+      </c>
+      <c r="N71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>72</v>
+      </c>
+      <c r="B72" t="str">
+        <v>["SUP-1066","Acme Logistics Solutions 66 LLC","con</v>
+      </c>
+      <c r="C72">
+        <v>20</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>21</v>
+      </c>
+      <c r="F72">
+        <v>5</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>-30</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>5</v>
+      </c>
+      <c r="M72">
+        <v>16</v>
+      </c>
+      <c r="N72">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>73</v>
+      </c>
+      <c r="B73" t="str">
+        <v>["SUP-1067","Acme Logistics Solutions 67 LLC","con</v>
+      </c>
+      <c r="C73">
+        <v>20</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>21</v>
+      </c>
+      <c r="F73">
+        <v>5</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>-30</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>5</v>
+      </c>
+      <c r="M73">
+        <v>16</v>
+      </c>
+      <c r="N73">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>74</v>
+      </c>
+      <c r="B74" t="str">
+        <v>["SUP-1068","Acme Logistics Solutions 68 LLC","con</v>
+      </c>
+      <c r="C74">
+        <v>20</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>21</v>
+      </c>
+      <c r="F74">
+        <v>5</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>-30</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>5</v>
+      </c>
+      <c r="M74">
+        <v>16</v>
+      </c>
+      <c r="N74">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>75</v>
+      </c>
+      <c r="B75" t="str">
+        <v>["SUP-1069","Acme Logistics Solutions 69 LLC","con</v>
+      </c>
+      <c r="C75">
+        <v>20</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>21</v>
+      </c>
+      <c r="F75">
+        <v>5</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>-30</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>5</v>
+      </c>
+      <c r="M75">
+        <v>16</v>
+      </c>
+      <c r="N75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>76</v>
+      </c>
+      <c r="B76" t="str">
+        <v>["SUP-1070","Acme Logistics Solutions 70 LLC","con</v>
+      </c>
+      <c r="C76">
+        <v>20</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>21</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>-30</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>5</v>
+      </c>
+      <c r="M76">
+        <v>16</v>
+      </c>
+      <c r="N76">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>77</v>
+      </c>
+      <c r="B77" t="str">
+        <v>["SUP-1071","Acme Logistics Solutions 71 LLC","con</v>
+      </c>
+      <c r="C77">
+        <v>20</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>21</v>
+      </c>
+      <c r="F77">
+        <v>5</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>-30</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>5</v>
+      </c>
+      <c r="M77">
+        <v>16</v>
+      </c>
+      <c r="N77">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>78</v>
+      </c>
+      <c r="B78" t="str">
+        <v>["SUP-1072","Acme Logistics Solutions 72 LLC","con</v>
+      </c>
+      <c r="C78">
+        <v>20</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>21</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>-30</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>5</v>
+      </c>
+      <c r="M78">
+        <v>16</v>
+      </c>
+      <c r="N78">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>79</v>
+      </c>
+      <c r="B79" t="str">
+        <v>["SUP-1073","Acme Logistics Solutions 73 LLC","con</v>
+      </c>
+      <c r="C79">
+        <v>20</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>21</v>
+      </c>
+      <c r="F79">
+        <v>5</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>-30</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>5</v>
+      </c>
+      <c r="M79">
+        <v>16</v>
+      </c>
+      <c r="N79">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="B80" t="str">
+        <v>["SUP-1074","Acme Logistics Solutions 74 LLC","con</v>
+      </c>
+      <c r="C80">
+        <v>20</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>21</v>
+      </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>-30</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>5</v>
+      </c>
+      <c r="M80">
+        <v>16</v>
+      </c>
+      <c r="N80">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>81</v>
+      </c>
+      <c r="B81" t="str">
+        <v>["SUP-1075","Acme Logistics Solutions 75 LLC","con</v>
+      </c>
+      <c r="C81">
+        <v>20</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>21</v>
+      </c>
+      <c r="F81">
+        <v>5</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>-30</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>5</v>
+      </c>
+      <c r="M81">
+        <v>16</v>
+      </c>
+      <c r="N81">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>82</v>
+      </c>
+      <c r="B82" t="str">
+        <v>["SUP-1076","Acme Logistics Solutions 76 LLC","con</v>
+      </c>
+      <c r="C82">
+        <v>20</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>21</v>
+      </c>
+      <c r="F82">
+        <v>5</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>-30</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>5</v>
+      </c>
+      <c r="M82">
+        <v>16</v>
+      </c>
+      <c r="N82">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>83</v>
+      </c>
+      <c r="B83" t="str">
+        <v>["SUP-1077","Acme Logistics Solutions 77 LLC","con</v>
+      </c>
+      <c r="C83">
+        <v>20</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>21</v>
+      </c>
+      <c r="F83">
+        <v>5</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>-30</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>5</v>
+      </c>
+      <c r="M83">
+        <v>16</v>
+      </c>
+      <c r="N83">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>84</v>
+      </c>
+      <c r="B84" t="str">
+        <v>["SUP-1078","Acme Logistics Solutions 78 LLC","con</v>
+      </c>
+      <c r="C84">
+        <v>20</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>21</v>
+      </c>
+      <c r="F84">
+        <v>5</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>-30</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>5</v>
+      </c>
+      <c r="M84">
+        <v>16</v>
+      </c>
+      <c r="N84">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>85</v>
+      </c>
+      <c r="B85" t="str">
+        <v>["SUP-1079","Acme Logistics Solutions 79 LLC","con</v>
+      </c>
+      <c r="C85">
+        <v>20</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>21</v>
+      </c>
+      <c r="F85">
+        <v>5</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>-30</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>5</v>
+      </c>
+      <c r="M85">
+        <v>16</v>
+      </c>
+      <c r="N85">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="str">
+        <v>["SUP-1080","Acme Logistics Solutions 80 LLC","con</v>
+      </c>
+      <c r="C86">
+        <v>20</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>21</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>-30</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>5</v>
+      </c>
+      <c r="M86">
+        <v>16</v>
+      </c>
+      <c r="N86">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="B87" t="str">
+        <v>["SUP-1081","Acme Logistics Solutions 81 LLC","con</v>
+      </c>
+      <c r="C87">
+        <v>20</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>21</v>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>-30</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>5</v>
+      </c>
+      <c r="M87">
+        <v>16</v>
+      </c>
+      <c r="N87">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="str">
+        <v>["SUP-1082","Acme Logistics Solutions 82 LLC","con</v>
+      </c>
+      <c r="C88">
+        <v>20</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>21</v>
+      </c>
+      <c r="F88">
+        <v>5</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>-30</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>5</v>
+      </c>
+      <c r="M88">
+        <v>16</v>
+      </c>
+      <c r="N88">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="str">
+        <v>["SUP-1083","Acme Logistics Solutions 83 LLC","con</v>
+      </c>
+      <c r="C89">
+        <v>20</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>21</v>
+      </c>
+      <c r="F89">
+        <v>5</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>-30</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>5</v>
+      </c>
+      <c r="M89">
+        <v>16</v>
+      </c>
+      <c r="N89">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>90</v>
+      </c>
+      <c r="B90" t="str">
+        <v>["SUP-1084","Acme Logistics Solutions 84 LLC","con</v>
+      </c>
+      <c r="C90">
+        <v>20</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>21</v>
+      </c>
+      <c r="F90">
+        <v>5</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>-30</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>5</v>
+      </c>
+      <c r="M90">
+        <v>16</v>
+      </c>
+      <c r="N90">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>91</v>
+      </c>
+      <c r="B91" t="str">
+        <v>["SUP-1085","Acme Logistics Solutions 85 LLC","con</v>
+      </c>
+      <c r="C91">
+        <v>20</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>21</v>
+      </c>
+      <c r="F91">
+        <v>5</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>-30</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>5</v>
+      </c>
+      <c r="M91">
+        <v>16</v>
+      </c>
+      <c r="N91">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>92</v>
+      </c>
+      <c r="B92" t="str">
+        <v>["SUP-1086","Acme Logistics Solutions 86 LLC","con</v>
+      </c>
+      <c r="C92">
+        <v>20</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>21</v>
+      </c>
+      <c r="F92">
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>-30</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>5</v>
+      </c>
+      <c r="M92">
+        <v>16</v>
+      </c>
+      <c r="N92">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>93</v>
+      </c>
+      <c r="B93" t="str">
+        <v>["SUP-1087","Acme Logistics Solutions 87 LLC","con</v>
+      </c>
+      <c r="C93">
+        <v>20</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>21</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>-30</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>5</v>
+      </c>
+      <c r="M93">
+        <v>16</v>
+      </c>
+      <c r="N93">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94" t="str">
+        <v>["SUP-1088","Acme Logistics Solutions 88 LLC","con</v>
+      </c>
+      <c r="C94">
+        <v>20</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>21</v>
+      </c>
+      <c r="F94">
+        <v>5</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>-30</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>5</v>
+      </c>
+      <c r="M94">
+        <v>16</v>
+      </c>
+      <c r="N94">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="B95" t="str">
+        <v>["SUP-1089","Acme Logistics Solutions 89 LLC","con</v>
+      </c>
+      <c r="C95">
+        <v>20</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>21</v>
+      </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>-30</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>5</v>
+      </c>
+      <c r="M95">
+        <v>16</v>
+      </c>
+      <c r="N95">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>96</v>
+      </c>
+      <c r="B96" t="str">
+        <v>["SUP-1090","Acme Logistics Solutions 90 LLC","con</v>
+      </c>
+      <c r="C96">
+        <v>20</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>21</v>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>-30</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>5</v>
+      </c>
+      <c r="M96">
+        <v>16</v>
+      </c>
+      <c r="N96">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="B97" t="str">
+        <v>["SUP-1091","Acme Logistics Solutions 91 LLC","con</v>
+      </c>
+      <c r="C97">
+        <v>20</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>21</v>
+      </c>
+      <c r="F97">
+        <v>5</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>-30</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>5</v>
+      </c>
+      <c r="M97">
+        <v>16</v>
+      </c>
+      <c r="N97">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="str">
+        <v>["SUP-1092","Acme Logistics Solutions 92 LLC","con</v>
+      </c>
+      <c r="C98">
+        <v>20</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>21</v>
+      </c>
+      <c r="F98">
+        <v>5</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>-30</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>5</v>
+      </c>
+      <c r="M98">
+        <v>16</v>
+      </c>
+      <c r="N98">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="str">
+        <v>["SUP-1093","Acme Logistics Solutions 93 LLC","con</v>
+      </c>
+      <c r="C99">
+        <v>20</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>21</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>-30</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>5</v>
+      </c>
+      <c r="M99">
+        <v>16</v>
+      </c>
+      <c r="N99">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="str">
+        <v>["SUP-1094","Acme Logistics Solutions 94 LLC","con</v>
+      </c>
+      <c r="C100">
+        <v>20</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>21</v>
+      </c>
+      <c r="F100">
+        <v>5</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>-30</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>5</v>
+      </c>
+      <c r="M100">
+        <v>16</v>
+      </c>
+      <c r="N100">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>101</v>
+      </c>
+      <c r="B101" t="str">
+        <v>["SUP-1095","Acme Logistics Solutions 95 LLC","con</v>
+      </c>
+      <c r="C101">
+        <v>20</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>21</v>
+      </c>
+      <c r="F101">
+        <v>5</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>-30</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>5</v>
+      </c>
+      <c r="M101">
+        <v>16</v>
+      </c>
+      <c r="N101">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>102</v>
+      </c>
+      <c r="B102" t="str">
+        <v>["SUP-1096","Acme Logistics Solutions 96 LLC","con</v>
+      </c>
+      <c r="C102">
+        <v>20</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>21</v>
+      </c>
+      <c r="F102">
+        <v>5</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>-30</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>5</v>
+      </c>
+      <c r="M102">
+        <v>16</v>
+      </c>
+      <c r="N102">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>103</v>
+      </c>
+      <c r="B103" t="str">
+        <v>["SUP-1097","Acme Logistics Solutions 97 LLC","con</v>
+      </c>
+      <c r="C103">
+        <v>20</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>21</v>
+      </c>
+      <c r="F103">
+        <v>5</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>-30</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>5</v>
+      </c>
+      <c r="M103">
+        <v>16</v>
+      </c>
+      <c r="N103">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>104</v>
+      </c>
+      <c r="B104" t="str">
+        <v>["SUP-1098","Acme Logistics Solutions 98 LLC","con</v>
+      </c>
+      <c r="C104">
+        <v>20</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>21</v>
+      </c>
+      <c r="F104">
+        <v>5</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>-30</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>5</v>
+      </c>
+      <c r="M104">
+        <v>16</v>
+      </c>
+      <c r="N104">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>105</v>
+      </c>
+      <c r="B105" t="str">
+        <v>["SUP-1099","Acme Logistics Solutions 99 LLC","con</v>
+      </c>
+      <c r="C105">
+        <v>20</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>21</v>
+      </c>
+      <c r="F105">
+        <v>5</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>-30</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>5</v>
+      </c>
+      <c r="M105">
+        <v>16</v>
+      </c>
+      <c r="N105">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>106</v>
+      </c>
+      <c r="B106" t="str">
+        <v>["SUP-1100","Acme Logistics Solutions 100 LLC","co</v>
+      </c>
+      <c r="C106">
+        <v>20</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>21</v>
+      </c>
+      <c r="F106">
+        <v>5</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>-30</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>5</v>
+      </c>
+      <c r="M106">
+        <v>16</v>
+      </c>
+      <c r="N106">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>107</v>
+      </c>
+      <c r="B107" t="str">
+        <v>["SUP-1101","Acme Logistics Solutions 101 LLC","co</v>
+      </c>
+      <c r="C107">
+        <v>20</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>21</v>
+      </c>
+      <c r="F107">
+        <v>5</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>-30</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>5</v>
+      </c>
+      <c r="M107">
+        <v>16</v>
+      </c>
+      <c r="N107">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>108</v>
+      </c>
+      <c r="B108" t="str">
+        <v>["SUP-1102","Acme Logistics Solutions 102 LLC","co</v>
+      </c>
+      <c r="C108">
+        <v>20</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>21</v>
+      </c>
+      <c r="F108">
+        <v>5</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>-30</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>5</v>
+      </c>
+      <c r="M108">
+        <v>16</v>
+      </c>
+      <c r="N108">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>109</v>
+      </c>
+      <c r="B109" t="str">
+        <v>["SUP-1103","Acme Logistics Solutions 103 LLC","co</v>
+      </c>
+      <c r="C109">
+        <v>20</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>21</v>
+      </c>
+      <c r="F109">
+        <v>5</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>-30</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>5</v>
+      </c>
+      <c r="M109">
+        <v>16</v>
+      </c>
+      <c r="N109">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>110</v>
+      </c>
+      <c r="B110" t="str">
+        <v>["SUP-1104","Acme Logistics Solutions 104 LLC","co</v>
+      </c>
+      <c r="C110">
+        <v>20</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>21</v>
+      </c>
+      <c r="F110">
+        <v>5</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>-30</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>5</v>
+      </c>
+      <c r="M110">
+        <v>16</v>
+      </c>
+      <c r="N110">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>111</v>
+      </c>
+      <c r="B111" t="str">
+        <v>["SUP-1105","Acme Logistics Solutions 105 LLC","co</v>
+      </c>
+      <c r="C111">
+        <v>20</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>21</v>
+      </c>
+      <c r="F111">
+        <v>5</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>-30</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>5</v>
+      </c>
+      <c r="M111">
+        <v>16</v>
+      </c>
+      <c r="N111">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>112</v>
+      </c>
+      <c r="B112" t="str">
+        <v>["SUP-1106","Acme Logistics Solutions 106 LLC","co</v>
+      </c>
+      <c r="C112">
+        <v>20</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>21</v>
+      </c>
+      <c r="F112">
+        <v>5</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>-30</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>5</v>
+      </c>
+      <c r="M112">
+        <v>16</v>
+      </c>
+      <c r="N112">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>113</v>
+      </c>
+      <c r="B113" t="str">
+        <v>["SUP-1107","Acme Logistics Solutions 107 LLC","co</v>
+      </c>
+      <c r="C113">
+        <v>20</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>21</v>
+      </c>
+      <c r="F113">
+        <v>5</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>-30</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>5</v>
+      </c>
+      <c r="M113">
+        <v>16</v>
+      </c>
+      <c r="N113">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>114</v>
+      </c>
+      <c r="B114" t="str">
+        <v>["SUP-1108","Acme Logistics Solutions 108 LLC","co</v>
+      </c>
+      <c r="C114">
+        <v>20</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>21</v>
+      </c>
+      <c r="F114">
+        <v>5</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>-30</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>5</v>
+      </c>
+      <c r="M114">
+        <v>16</v>
+      </c>
+      <c r="N114">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>115</v>
+      </c>
+      <c r="B115" t="str">
+        <v>["SUP-1109","Acme Logistics Solutions 109 LLC","co</v>
+      </c>
+      <c r="C115">
+        <v>20</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>21</v>
+      </c>
+      <c r="F115">
+        <v>5</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>-30</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>5</v>
+      </c>
+      <c r="M115">
+        <v>16</v>
+      </c>
+      <c r="N115">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>116</v>
+      </c>
+      <c r="B116" t="str">
+        <v>["SUP-1110","Acme Logistics Solutions 110 LLC","co</v>
+      </c>
+      <c r="C116">
+        <v>20</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>21</v>
+      </c>
+      <c r="F116">
+        <v>5</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>-30</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>5</v>
+      </c>
+      <c r="M116">
+        <v>16</v>
+      </c>
+      <c r="N116">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>117</v>
+      </c>
+      <c r="B117" t="str">
+        <v>["SUP-1111","Acme Logistics Solutions 111 LLC","co</v>
+      </c>
+      <c r="C117">
+        <v>20</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>21</v>
+      </c>
+      <c r="F117">
+        <v>5</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>-30</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>5</v>
+      </c>
+      <c r="M117">
+        <v>16</v>
+      </c>
+      <c r="N117">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>118</v>
+      </c>
+      <c r="B118" t="str">
+        <v>["SUP-1112","Acme Logistics Solutions 112 LLC","co</v>
+      </c>
+      <c r="C118">
+        <v>20</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>21</v>
+      </c>
+      <c r="F118">
+        <v>5</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>-30</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>5</v>
+      </c>
+      <c r="M118">
+        <v>16</v>
+      </c>
+      <c r="N118">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>119</v>
+      </c>
+      <c r="B119" t="str">
+        <v>["SUP-1113","Acme Logistics Solutions 113 LLC","co</v>
+      </c>
+      <c r="C119">
+        <v>20</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>21</v>
+      </c>
+      <c r="F119">
+        <v>5</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>-30</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>5</v>
+      </c>
+      <c r="M119">
+        <v>16</v>
+      </c>
+      <c r="N119">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>120</v>
+      </c>
+      <c r="B120" t="str">
+        <v>["SUP-1114","Acme Logistics Solutions 114 LLC","co</v>
+      </c>
+      <c r="C120">
+        <v>20</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>21</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>-30</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>5</v>
+      </c>
+      <c r="M120">
+        <v>16</v>
+      </c>
+      <c r="N120">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>121</v>
+      </c>
+      <c r="B121" t="str">
+        <v>["SUP-1115","Acme Logistics Solutions 115 LLC","co</v>
+      </c>
+      <c r="C121">
+        <v>20</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>21</v>
+      </c>
+      <c r="F121">
+        <v>5</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>-30</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>5</v>
+      </c>
+      <c r="M121">
+        <v>16</v>
+      </c>
+      <c r="N121">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>122</v>
+      </c>
+      <c r="B122" t="str">
+        <v>["SUP-1116","Acme Logistics Solutions 116 LLC","co</v>
+      </c>
+      <c r="C122">
+        <v>20</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>21</v>
+      </c>
+      <c r="F122">
+        <v>5</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>-30</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>5</v>
+      </c>
+      <c r="M122">
+        <v>16</v>
+      </c>
+      <c r="N122">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>123</v>
+      </c>
+      <c r="B123" t="str">
+        <v>["SUP-1117","Acme Logistics Solutions 117 LLC","co</v>
+      </c>
+      <c r="C123">
+        <v>20</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>21</v>
+      </c>
+      <c r="F123">
+        <v>5</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>-30</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>5</v>
+      </c>
+      <c r="M123">
+        <v>16</v>
+      </c>
+      <c r="N123">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>124</v>
+      </c>
+      <c r="B124" t="str">
+        <v>["SUP-1118","Acme Logistics Solutions 118 LLC","co</v>
+      </c>
+      <c r="C124">
+        <v>20</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>21</v>
+      </c>
+      <c r="F124">
+        <v>5</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>-30</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>5</v>
+      </c>
+      <c r="M124">
+        <v>16</v>
+      </c>
+      <c r="N124">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>125</v>
+      </c>
+      <c r="B125" t="str">
+        <v>["SUP-1119","Acme Logistics Solutions 119 LLC","co</v>
+      </c>
+      <c r="C125">
+        <v>20</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>21</v>
+      </c>
+      <c r="F125">
+        <v>5</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>-30</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>5</v>
+      </c>
+      <c r="M125">
+        <v>16</v>
+      </c>
+      <c r="N125">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>126</v>
+      </c>
+      <c r="B126" t="str">
+        <v>["SUP-1120","Acme Logistics Solutions 120 LLC","co</v>
+      </c>
+      <c r="C126">
+        <v>20</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>21</v>
+      </c>
+      <c r="F126">
+        <v>5</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>-30</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>5</v>
+      </c>
+      <c r="M126">
+        <v>16</v>
+      </c>
+      <c r="N126">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>127</v>
+      </c>
+      <c r="B127" t="str">
+        <v>["SUP-1121","Acme Logistics Solutions 121 LLC","co</v>
+      </c>
+      <c r="C127">
+        <v>20</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>21</v>
+      </c>
+      <c r="F127">
+        <v>5</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>-30</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>5</v>
+      </c>
+      <c r="M127">
+        <v>16</v>
+      </c>
+      <c r="N127">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>128</v>
+      </c>
+      <c r="B128" t="str">
+        <v>["SUP-1122","Acme Logistics Solutions 122 LLC","co</v>
+      </c>
+      <c r="C128">
+        <v>20</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>21</v>
+      </c>
+      <c r="F128">
+        <v>5</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>-30</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>5</v>
+      </c>
+      <c r="M128">
+        <v>16</v>
+      </c>
+      <c r="N128">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>129</v>
+      </c>
+      <c r="B129" t="str">
+        <v>["SUP-1123","Acme Logistics Solutions 123 LLC","co</v>
+      </c>
+      <c r="C129">
+        <v>20</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>21</v>
+      </c>
+      <c r="F129">
+        <v>5</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>-30</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>5</v>
+      </c>
+      <c r="M129">
+        <v>16</v>
+      </c>
+      <c r="N129">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>130</v>
+      </c>
+      <c r="B130" t="str">
+        <v>["SUP-1124","Acme Logistics Solutions 124 LLC","co</v>
+      </c>
+      <c r="C130">
+        <v>20</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>21</v>
+      </c>
+      <c r="F130">
+        <v>5</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>-30</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>5</v>
+      </c>
+      <c r="M130">
+        <v>16</v>
+      </c>
+      <c r="N130">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>131</v>
+      </c>
+      <c r="B131" t="str">
+        <v>["SUP-1125","Acme Logistics Solutions 125 LLC","co</v>
+      </c>
+      <c r="C131">
+        <v>20</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>21</v>
+      </c>
+      <c r="F131">
+        <v>5</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>-30</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>5</v>
+      </c>
+      <c r="M131">
+        <v>16</v>
+      </c>
+      <c r="N131">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>132</v>
+      </c>
+      <c r="B132" t="str">
+        <v>["SUP-1126","Acme Logistics Solutions 126 LLC","co</v>
+      </c>
+      <c r="C132">
+        <v>20</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>21</v>
+      </c>
+      <c r="F132">
+        <v>5</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>-30</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>5</v>
+      </c>
+      <c r="M132">
+        <v>16</v>
+      </c>
+      <c r="N132">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>133</v>
+      </c>
+      <c r="B133" t="str">
+        <v>["SUP-1127","Acme Logistics Solutions 127 LLC","co</v>
+      </c>
+      <c r="C133">
+        <v>20</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>21</v>
+      </c>
+      <c r="F133">
+        <v>5</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>-30</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>5</v>
+      </c>
+      <c r="M133">
+        <v>16</v>
+      </c>
+      <c r="N133">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>134</v>
+      </c>
+      <c r="B134" t="str">
+        <v>["SUP-1128","Acme Logistics Solutions 128 LLC","co</v>
+      </c>
+      <c r="C134">
+        <v>20</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>21</v>
+      </c>
+      <c r="F134">
+        <v>5</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>-30</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>5</v>
+      </c>
+      <c r="M134">
+        <v>16</v>
+      </c>
+      <c r="N134">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>135</v>
+      </c>
+      <c r="B135" t="str">
+        <v>["SUP-1129","Acme Logistics Solutions 129 LLC","co</v>
+      </c>
+      <c r="C135">
+        <v>20</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>21</v>
+      </c>
+      <c r="F135">
+        <v>5</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>-30</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>5</v>
+      </c>
+      <c r="M135">
+        <v>16</v>
+      </c>
+      <c r="N135">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>136</v>
+      </c>
+      <c r="B136" t="str">
+        <v>["SUP-1130","Acme Logistics Solutions 130 LLC","co</v>
+      </c>
+      <c r="C136">
+        <v>20</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>21</v>
+      </c>
+      <c r="F136">
+        <v>5</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>-30</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>5</v>
+      </c>
+      <c r="M136">
+        <v>16</v>
+      </c>
+      <c r="N136">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>137</v>
+      </c>
+      <c r="B137" t="str">
+        <v>["SUP-1131","Acme Logistics Solutions 131 LLC","co</v>
+      </c>
+      <c r="C137">
+        <v>20</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>21</v>
+      </c>
+      <c r="F137">
+        <v>5</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>-30</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>5</v>
+      </c>
+      <c r="M137">
+        <v>16</v>
+      </c>
+      <c r="N137">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>138</v>
+      </c>
+      <c r="B138" t="str">
+        <v>["SUP-1132","Acme Logistics Solutions 132 LLC","co</v>
+      </c>
+      <c r="C138">
+        <v>20</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>21</v>
+      </c>
+      <c r="F138">
+        <v>5</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>-30</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>5</v>
+      </c>
+      <c r="M138">
+        <v>16</v>
+      </c>
+      <c r="N138">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>139</v>
+      </c>
+      <c r="B139" t="str">
+        <v>["SUP-1133","Acme Logistics Solutions 133 LLC","co</v>
+      </c>
+      <c r="C139">
+        <v>20</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>21</v>
+      </c>
+      <c r="F139">
+        <v>5</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>-30</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>5</v>
+      </c>
+      <c r="M139">
+        <v>16</v>
+      </c>
+      <c r="N139">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>140</v>
+      </c>
+      <c r="B140" t="str">
+        <v>["SUP-1134","Acme Logistics Solutions 134 LLC","co</v>
+      </c>
+      <c r="C140">
+        <v>20</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>21</v>
+      </c>
+      <c r="F140">
+        <v>5</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>-30</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>5</v>
+      </c>
+      <c r="M140">
+        <v>16</v>
+      </c>
+      <c r="N140">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>141</v>
+      </c>
+      <c r="B141" t="str">
+        <v>["SUP-1135","Acme Logistics Solutions 135 LLC","co</v>
+      </c>
+      <c r="C141">
+        <v>20</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>21</v>
+      </c>
+      <c r="F141">
+        <v>5</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>-30</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>5</v>
+      </c>
+      <c r="M141">
+        <v>16</v>
+      </c>
+      <c r="N141">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>142</v>
+      </c>
+      <c r="B142" t="str">
+        <v>["SUP-1136","Acme Logistics Solutions 136 LLC","co</v>
+      </c>
+      <c r="C142">
+        <v>20</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>21</v>
+      </c>
+      <c r="F142">
+        <v>5</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>-30</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>5</v>
+      </c>
+      <c r="M142">
+        <v>16</v>
+      </c>
+      <c r="N142">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>143</v>
+      </c>
+      <c r="B143" t="str">
+        <v>["SUP-1137","Acme Logistics Solutions 137 LLC","co</v>
+      </c>
+      <c r="C143">
+        <v>20</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>21</v>
+      </c>
+      <c r="F143">
+        <v>5</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>-30</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>5</v>
+      </c>
+      <c r="M143">
+        <v>16</v>
+      </c>
+      <c r="N143">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>144</v>
+      </c>
+      <c r="B144" t="str">
+        <v>["SUP-1138","Acme Logistics Solutions 138 LLC","co</v>
+      </c>
+      <c r="C144">
+        <v>20</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>21</v>
+      </c>
+      <c r="F144">
+        <v>5</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>-30</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>5</v>
+      </c>
+      <c r="M144">
+        <v>16</v>
+      </c>
+      <c r="N144">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>145</v>
+      </c>
+      <c r="B145" t="str">
+        <v>["SUP-1139","Acme Logistics Solutions 139 LLC","co</v>
+      </c>
+      <c r="C145">
+        <v>20</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>21</v>
+      </c>
+      <c r="F145">
+        <v>5</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>-30</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>5</v>
+      </c>
+      <c r="M145">
+        <v>16</v>
+      </c>
+      <c r="N145">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>146</v>
+      </c>
+      <c r="B146" t="str">
+        <v>["SUP-1140","Acme Logistics Solutions 140 LLC","co</v>
+      </c>
+      <c r="C146">
+        <v>20</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>21</v>
+      </c>
+      <c r="F146">
+        <v>5</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>-30</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>5</v>
+      </c>
+      <c r="M146">
+        <v>16</v>
+      </c>
+      <c r="N146">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>147</v>
+      </c>
+      <c r="B147" t="str">
+        <v>["SUP-1141","Acme Logistics Solutions 141 LLC","co</v>
+      </c>
+      <c r="C147">
+        <v>20</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>21</v>
+      </c>
+      <c r="F147">
+        <v>5</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>-30</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>5</v>
+      </c>
+      <c r="M147">
+        <v>16</v>
+      </c>
+      <c r="N147">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>148</v>
+      </c>
+      <c r="B148" t="str">
+        <v>["SUP-1142","Acme Logistics Solutions 142 LLC","co</v>
+      </c>
+      <c r="C148">
+        <v>20</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>21</v>
+      </c>
+      <c r="F148">
+        <v>5</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>-30</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>5</v>
+      </c>
+      <c r="M148">
+        <v>16</v>
+      </c>
+      <c r="N148">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>149</v>
+      </c>
+      <c r="B149" t="str">
+        <v>["SUP-1143","Acme Logistics Solutions 143 LLC","co</v>
+      </c>
+      <c r="C149">
+        <v>20</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>21</v>
+      </c>
+      <c r="F149">
+        <v>5</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>-30</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>5</v>
+      </c>
+      <c r="M149">
+        <v>16</v>
+      </c>
+      <c r="N149">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>150</v>
+      </c>
+      <c r="B150" t="str">
+        <v>["SUP-1144","Acme Logistics Solutions 144 LLC","co</v>
+      </c>
+      <c r="C150">
+        <v>20</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>21</v>
+      </c>
+      <c r="F150">
+        <v>5</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>-30</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>5</v>
+      </c>
+      <c r="M150">
+        <v>16</v>
+      </c>
+      <c r="N150">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>151</v>
+      </c>
+      <c r="B151" t="str">
+        <v>["SUP-1145","Acme Logistics Solutions 145 LLC","co</v>
+      </c>
+      <c r="C151">
+        <v>20</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>21</v>
+      </c>
+      <c r="F151">
+        <v>5</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>-30</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>5</v>
+      </c>
+      <c r="M151">
+        <v>16</v>
+      </c>
+      <c r="N151">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>152</v>
+      </c>
+      <c r="B152" t="str">
+        <v>["SUP-1146","Acme Logistics Solutions 146 LLC","co</v>
+      </c>
+      <c r="C152">
+        <v>20</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>21</v>
+      </c>
+      <c r="F152">
+        <v>5</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>-30</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>5</v>
+      </c>
+      <c r="M152">
+        <v>16</v>
+      </c>
+      <c r="N152">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>153</v>
+      </c>
+      <c r="B153" t="str">
+        <v>["SUP-1147","Acme Logistics Solutions 147 LLC","co</v>
+      </c>
+      <c r="C153">
+        <v>20</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>21</v>
+      </c>
+      <c r="F153">
+        <v>5</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>-30</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>5</v>
+      </c>
+      <c r="M153">
+        <v>16</v>
+      </c>
+      <c r="N153">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>154</v>
+      </c>
+      <c r="B154" t="str">
+        <v>["SUP-1148","Acme Logistics Solutions 148 LLC","co</v>
+      </c>
+      <c r="C154">
+        <v>20</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>21</v>
+      </c>
+      <c r="F154">
+        <v>5</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>-30</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>5</v>
+      </c>
+      <c r="M154">
+        <v>16</v>
+      </c>
+      <c r="N154">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>155</v>
+      </c>
+      <c r="B155" t="str">
+        <v>["SUP-1149","Acme Logistics Solutions 149 LLC","co</v>
+      </c>
+      <c r="C155">
+        <v>20</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>21</v>
+      </c>
+      <c r="F155">
+        <v>5</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>-30</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>5</v>
+      </c>
+      <c r="M155">
+        <v>16</v>
+      </c>
+      <c r="N155">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>156</v>
+      </c>
+      <c r="B156" t="str">
+        <v>["SUP-1150","Acme Logistics Solutions 150 LLC","co</v>
+      </c>
+      <c r="C156">
+        <v>20</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>21</v>
+      </c>
+      <c r="F156">
+        <v>5</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>-30</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>5</v>
+      </c>
+      <c r="M156">
+        <v>16</v>
+      </c>
+      <c r="N156">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>157</v>
+      </c>
+      <c r="B157" t="str">
+        <v>["SUP-1151","Acme Logistics Solutions 151 LLC","co</v>
+      </c>
+      <c r="C157">
+        <v>20</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>21</v>
+      </c>
+      <c r="F157">
+        <v>5</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>-30</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>5</v>
+      </c>
+      <c r="M157">
+        <v>16</v>
+      </c>
+      <c r="N157">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>158</v>
+      </c>
+      <c r="B158" t="str">
+        <v>["SUP-1152","Acme Logistics Solutions 152 LLC","co</v>
+      </c>
+      <c r="C158">
+        <v>20</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>21</v>
+      </c>
+      <c r="F158">
+        <v>5</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>-30</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>5</v>
+      </c>
+      <c r="M158">
+        <v>16</v>
+      </c>
+      <c r="N158">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>159</v>
+      </c>
+      <c r="B159" t="str">
+        <v>["SUP-1153","Acme Logistics Solutions 153 LLC","co</v>
+      </c>
+      <c r="C159">
+        <v>20</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>21</v>
+      </c>
+      <c r="F159">
+        <v>5</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>-30</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>5</v>
+      </c>
+      <c r="M159">
+        <v>16</v>
+      </c>
+      <c r="N159">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>160</v>
+      </c>
+      <c r="B160" t="str">
+        <v>["SUP-1154","Acme Logistics Solutions 154 LLC","co</v>
+      </c>
+      <c r="C160">
+        <v>20</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>21</v>
+      </c>
+      <c r="F160">
+        <v>5</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>-30</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>5</v>
+      </c>
+      <c r="M160">
+        <v>16</v>
+      </c>
+      <c r="N160">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>161</v>
+      </c>
+      <c r="B161" t="str">
+        <v>["SUP-1155","Acme Logistics Solutions 155 LLC","co</v>
+      </c>
+      <c r="C161">
+        <v>20</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>21</v>
+      </c>
+      <c r="F161">
+        <v>5</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>-30</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>5</v>
+      </c>
+      <c r="M161">
+        <v>16</v>
+      </c>
+      <c r="N161">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>162</v>
+      </c>
+      <c r="B162" t="str">
+        <v>["SUP-1156","Acme Logistics Solutions 156 LLC","co</v>
+      </c>
+      <c r="C162">
+        <v>20</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>21</v>
+      </c>
+      <c r="F162">
+        <v>5</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>-30</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>5</v>
+      </c>
+      <c r="M162">
+        <v>16</v>
+      </c>
+      <c r="N162">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>163</v>
+      </c>
+      <c r="B163" t="str">
+        <v>["SUP-1157","Acme Logistics Solutions 157 LLC","co</v>
+      </c>
+      <c r="C163">
+        <v>20</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>21</v>
+      </c>
+      <c r="F163">
+        <v>5</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>-30</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>5</v>
+      </c>
+      <c r="M163">
+        <v>16</v>
+      </c>
+      <c r="N163">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>164</v>
+      </c>
+      <c r="B164" t="str">
+        <v>["SUP-1158","Acme Logistics Solutions 158 LLC","co</v>
+      </c>
+      <c r="C164">
+        <v>20</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>21</v>
+      </c>
+      <c r="F164">
+        <v>5</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>-30</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>5</v>
+      </c>
+      <c r="M164">
+        <v>16</v>
+      </c>
+      <c r="N164">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>165</v>
+      </c>
+      <c r="B165" t="str">
+        <v>["SUP-1159","Acme Logistics Solutions 159 LLC","co</v>
+      </c>
+      <c r="C165">
+        <v>20</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>21</v>
+      </c>
+      <c r="F165">
+        <v>5</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>-30</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>5</v>
+      </c>
+      <c r="M165">
+        <v>16</v>
+      </c>
+      <c r="N165">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>166</v>
+      </c>
+      <c r="B166" t="str">
+        <v>["SUP-1160","Acme Logistics Solutions 160 LLC","co</v>
+      </c>
+      <c r="C166">
+        <v>20</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>21</v>
+      </c>
+      <c r="F166">
+        <v>5</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>-30</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>5</v>
+      </c>
+      <c r="M166">
+        <v>16</v>
+      </c>
+      <c r="N166">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>167</v>
+      </c>
+      <c r="B167" t="str">
+        <v>["SUP-1161","Acme Logistics Solutions 161 LLC","co</v>
+      </c>
+      <c r="C167">
+        <v>20</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>21</v>
+      </c>
+      <c r="F167">
+        <v>5</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>-30</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>5</v>
+      </c>
+      <c r="M167">
+        <v>16</v>
+      </c>
+      <c r="N167">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>168</v>
+      </c>
+      <c r="B168" t="str">
+        <v>["SUP-1162","Acme Logistics Solutions 162 LLC","co</v>
+      </c>
+      <c r="C168">
+        <v>20</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>21</v>
+      </c>
+      <c r="F168">
+        <v>5</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>-30</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>5</v>
+      </c>
+      <c r="M168">
+        <v>16</v>
+      </c>
+      <c r="N168">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>169</v>
+      </c>
+      <c r="B169" t="str">
+        <v>["SUP-1163","Acme Logistics Solutions 163 LLC","co</v>
+      </c>
+      <c r="C169">
+        <v>20</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>21</v>
+      </c>
+      <c r="F169">
+        <v>5</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>-30</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>5</v>
+      </c>
+      <c r="M169">
+        <v>16</v>
+      </c>
+      <c r="N169">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>170</v>
+      </c>
+      <c r="B170" t="str">
+        <v>["SUP-1164","Acme Logistics Solutions 164 LLC","co</v>
+      </c>
+      <c r="C170">
+        <v>20</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>21</v>
+      </c>
+      <c r="F170">
+        <v>5</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>-30</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>5</v>
+      </c>
+      <c r="M170">
+        <v>16</v>
+      </c>
+      <c r="N170">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>171</v>
+      </c>
+      <c r="B171" t="str">
+        <v>["SUP-1165","Acme Logistics Solutions 165 LLC","co</v>
+      </c>
+      <c r="C171">
+        <v>20</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>21</v>
+      </c>
+      <c r="F171">
+        <v>5</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>-30</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>5</v>
+      </c>
+      <c r="M171">
+        <v>16</v>
+      </c>
+      <c r="N171">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>172</v>
+      </c>
+      <c r="B172" t="str">
+        <v>["SUP-1166","Acme Logistics Solutions 166 LLC","co</v>
+      </c>
+      <c r="C172">
+        <v>20</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>21</v>
+      </c>
+      <c r="F172">
+        <v>5</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>-30</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>5</v>
+      </c>
+      <c r="M172">
+        <v>16</v>
+      </c>
+      <c r="N172">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>173</v>
+      </c>
+      <c r="B173" t="str">
+        <v>["SUP-1167","Acme Logistics Solutions 167 LLC","co</v>
+      </c>
+      <c r="C173">
+        <v>20</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>21</v>
+      </c>
+      <c r="F173">
+        <v>5</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>-30</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>5</v>
+      </c>
+      <c r="M173">
+        <v>16</v>
+      </c>
+      <c r="N173">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>174</v>
+      </c>
+      <c r="B174" t="str">
+        <v>["SUP-1168","Acme Logistics Solutions 168 LLC","co</v>
+      </c>
+      <c r="C174">
+        <v>20</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>21</v>
+      </c>
+      <c r="F174">
+        <v>5</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>-30</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>5</v>
+      </c>
+      <c r="M174">
+        <v>16</v>
+      </c>
+      <c r="N174">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>175</v>
+      </c>
+      <c r="B175" t="str">
+        <v>["SUP-1169","Acme Logistics Solutions 169 LLC","co</v>
+      </c>
+      <c r="C175">
+        <v>20</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>21</v>
+      </c>
+      <c r="F175">
+        <v>5</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>-30</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>5</v>
+      </c>
+      <c r="M175">
+        <v>16</v>
+      </c>
+      <c r="N175">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>176</v>
+      </c>
+      <c r="B176" t="str">
+        <v>["SUP-1170","Acme Logistics Solutions 170 LLC","co</v>
+      </c>
+      <c r="C176">
+        <v>20</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>21</v>
+      </c>
+      <c r="F176">
+        <v>5</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>-30</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>5</v>
+      </c>
+      <c r="M176">
+        <v>16</v>
+      </c>
+      <c r="N176">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>177</v>
+      </c>
+      <c r="B177" t="str">
+        <v>["SUP-1171","Acme Logistics Solutions 171 LLC","co</v>
+      </c>
+      <c r="C177">
+        <v>20</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>21</v>
+      </c>
+      <c r="F177">
+        <v>5</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>-30</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>5</v>
+      </c>
+      <c r="M177">
+        <v>16</v>
+      </c>
+      <c r="N177">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>178</v>
+      </c>
+      <c r="B178" t="str">
+        <v>["SUP-1172","Acme Logistics Solutions 172 LLC","co</v>
+      </c>
+      <c r="C178">
+        <v>20</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>21</v>
+      </c>
+      <c r="F178">
+        <v>5</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>-30</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>5</v>
+      </c>
+      <c r="M178">
+        <v>16</v>
+      </c>
+      <c r="N178">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>179</v>
+      </c>
+      <c r="B179" t="str">
+        <v>["SUP-1173","Acme Logistics Solutions 173 LLC","co</v>
+      </c>
+      <c r="C179">
+        <v>20</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>21</v>
+      </c>
+      <c r="F179">
+        <v>5</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>-30</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>5</v>
+      </c>
+      <c r="M179">
+        <v>16</v>
+      </c>
+      <c r="N179">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>180</v>
+      </c>
+      <c r="B180" t="str">
+        <v>["SUP-1174","Acme Logistics Solutions 174 LLC","co</v>
+      </c>
+      <c r="C180">
+        <v>20</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>21</v>
+      </c>
+      <c r="F180">
+        <v>5</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>-30</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>5</v>
+      </c>
+      <c r="M180">
+        <v>16</v>
+      </c>
+      <c r="N180">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>181</v>
+      </c>
+      <c r="B181" t="str">
+        <v>["SUP-1175","Acme Logistics Solutions 175 LLC","co</v>
+      </c>
+      <c r="C181">
+        <v>20</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>21</v>
+      </c>
+      <c r="F181">
+        <v>5</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>-30</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>5</v>
+      </c>
+      <c r="M181">
+        <v>16</v>
+      </c>
+      <c r="N181">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>182</v>
+      </c>
+      <c r="B182" t="str">
+        <v>["SUP-1176","Acme Logistics Solutions 176 LLC","co</v>
+      </c>
+      <c r="C182">
+        <v>20</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>21</v>
+      </c>
+      <c r="F182">
+        <v>5</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>-30</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>5</v>
+      </c>
+      <c r="M182">
+        <v>16</v>
+      </c>
+      <c r="N182">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>183</v>
+      </c>
+      <c r="B183" t="str">
+        <v>["SUP-1177","Acme Logistics Solutions 177 LLC","co</v>
+      </c>
+      <c r="C183">
+        <v>20</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>21</v>
+      </c>
+      <c r="F183">
+        <v>5</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>-30</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>5</v>
+      </c>
+      <c r="M183">
+        <v>16</v>
+      </c>
+      <c r="N183">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>184</v>
+      </c>
+      <c r="B184" t="str">
+        <v>["SUP-1178","Acme Logistics Solutions 178 LLC","co</v>
+      </c>
+      <c r="C184">
+        <v>20</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>21</v>
+      </c>
+      <c r="F184">
+        <v>5</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>-30</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>5</v>
+      </c>
+      <c r="M184">
+        <v>16</v>
+      </c>
+      <c r="N184">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>185</v>
+      </c>
+      <c r="B185" t="str">
+        <v>["SUP-1179","Acme Logistics Solutions 179 LLC","co</v>
+      </c>
+      <c r="C185">
+        <v>20</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>21</v>
+      </c>
+      <c r="F185">
+        <v>5</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>-30</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>5</v>
+      </c>
+      <c r="M185">
+        <v>16</v>
+      </c>
+      <c r="N185">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>186</v>
+      </c>
+      <c r="B186" t="str">
+        <v>["SUP-1180","Acme Logistics Solutions 180 LLC","co</v>
+      </c>
+      <c r="C186">
+        <v>20</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>21</v>
+      </c>
+      <c r="F186">
+        <v>5</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>-30</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>5</v>
+      </c>
+      <c r="M186">
+        <v>16</v>
+      </c>
+      <c r="N186">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>187</v>
+      </c>
+      <c r="B187" t="str">
+        <v>["SUP-1181","Acme Logistics Solutions 181 LLC","co</v>
+      </c>
+      <c r="C187">
+        <v>20</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>21</v>
+      </c>
+      <c r="F187">
+        <v>5</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>-30</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>5</v>
+      </c>
+      <c r="M187">
+        <v>16</v>
+      </c>
+      <c r="N187">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>188</v>
+      </c>
+      <c r="B188" t="str">
+        <v>["SUP-1182","Acme Logistics Solutions 182 LLC","co</v>
+      </c>
+      <c r="C188">
+        <v>20</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>21</v>
+      </c>
+      <c r="F188">
+        <v>5</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>-30</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>5</v>
+      </c>
+      <c r="M188">
+        <v>16</v>
+      </c>
+      <c r="N188">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>189</v>
+      </c>
+      <c r="B189" t="str">
+        <v>["SUP-1183","Acme Logistics Solutions 183 LLC","co</v>
+      </c>
+      <c r="C189">
+        <v>20</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>21</v>
+      </c>
+      <c r="F189">
+        <v>5</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>-30</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>5</v>
+      </c>
+      <c r="M189">
+        <v>16</v>
+      </c>
+      <c r="N189">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>190</v>
+      </c>
+      <c r="B190" t="str">
+        <v>["SUP-1184","Acme Logistics Solutions 184 LLC","co</v>
+      </c>
+      <c r="C190">
+        <v>20</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>21</v>
+      </c>
+      <c r="F190">
+        <v>5</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>-30</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>5</v>
+      </c>
+      <c r="M190">
+        <v>16</v>
+      </c>
+      <c r="N190">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>191</v>
+      </c>
+      <c r="B191" t="str">
+        <v>["SUP-1185","Acme Logistics Solutions 185 LLC","co</v>
+      </c>
+      <c r="C191">
+        <v>20</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>21</v>
+      </c>
+      <c r="F191">
+        <v>5</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>-30</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>5</v>
+      </c>
+      <c r="M191">
+        <v>16</v>
+      </c>
+      <c r="N191">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>192</v>
+      </c>
+      <c r="B192" t="str">
+        <v>["SUP-1186","Acme Logistics Solutions 186 LLC","co</v>
+      </c>
+      <c r="C192">
+        <v>20</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>21</v>
+      </c>
+      <c r="F192">
+        <v>5</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>-30</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>5</v>
+      </c>
+      <c r="M192">
+        <v>16</v>
+      </c>
+      <c r="N192">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>193</v>
+      </c>
+      <c r="B193" t="str">
+        <v>["SUP-1187","Acme Logistics Solutions 187 LLC","co</v>
+      </c>
+      <c r="C193">
+        <v>20</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <v>21</v>
+      </c>
+      <c r="F193">
+        <v>5</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>-30</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>5</v>
+      </c>
+      <c r="M193">
+        <v>16</v>
+      </c>
+      <c r="N193">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>194</v>
+      </c>
+      <c r="B194" t="str">
+        <v>["SUP-1188","Acme Logistics Solutions 188 LLC","co</v>
+      </c>
+      <c r="C194">
+        <v>20</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>21</v>
+      </c>
+      <c r="F194">
+        <v>5</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>-30</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>5</v>
+      </c>
+      <c r="M194">
+        <v>16</v>
+      </c>
+      <c r="N194">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>195</v>
+      </c>
+      <c r="B195" t="str">
+        <v>["SUP-1189","Acme Logistics Solutions 189 LLC","co</v>
+      </c>
+      <c r="C195">
+        <v>20</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>21</v>
+      </c>
+      <c r="F195">
+        <v>5</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>-30</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>5</v>
+      </c>
+      <c r="M195">
+        <v>16</v>
+      </c>
+      <c r="N195">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>196</v>
+      </c>
+      <c r="B196" t="str">
+        <v>["SUP-1190","Acme Logistics Solutions 190 LLC","co</v>
+      </c>
+      <c r="C196">
+        <v>20</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>21</v>
+      </c>
+      <c r="F196">
+        <v>5</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>-30</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>5</v>
+      </c>
+      <c r="M196">
+        <v>16</v>
+      </c>
+      <c r="N196">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>197</v>
+      </c>
+      <c r="B197" t="str">
+        <v>["SUP-1191","Acme Logistics Solutions 191 LLC","co</v>
+      </c>
+      <c r="C197">
+        <v>20</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>21</v>
+      </c>
+      <c r="F197">
+        <v>5</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>-30</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>5</v>
+      </c>
+      <c r="M197">
+        <v>16</v>
+      </c>
+      <c r="N197">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>198</v>
+      </c>
+      <c r="B198" t="str">
+        <v>["SUP-1192","Acme Logistics Solutions 192 LLC","co</v>
+      </c>
+      <c r="C198">
+        <v>20</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>21</v>
+      </c>
+      <c r="F198">
+        <v>5</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>-30</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>5</v>
+      </c>
+      <c r="M198">
+        <v>16</v>
+      </c>
+      <c r="N198">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>199</v>
+      </c>
+      <c r="B199" t="str">
+        <v>["SUP-1193","Acme Logistics Solutions 193 LLC","co</v>
+      </c>
+      <c r="C199">
+        <v>20</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>21</v>
+      </c>
+      <c r="F199">
+        <v>5</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>-30</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>5</v>
+      </c>
+      <c r="M199">
+        <v>16</v>
+      </c>
+      <c r="N199">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>200</v>
+      </c>
+      <c r="B200" t="str">
+        <v>["SUP-1194","Acme Logistics Solutions 194 LLC","co</v>
+      </c>
+      <c r="C200">
+        <v>20</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>21</v>
+      </c>
+      <c r="F200">
+        <v>5</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>-30</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>5</v>
+      </c>
+      <c r="M200">
+        <v>16</v>
+      </c>
+      <c r="N200">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/Large_Valid_Standard_Test.xlsx
+++ b/frontend/test_data/header_detection/Large_Valid_Standard_Test.xlsx
@@ -4606,7 +4606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:M200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4634,21 +4634,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -4684,15 +4681,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="M2">
-        <v>49</v>
-      </c>
-      <c r="N2">
         <v>49</v>
       </c>
     </row>
@@ -4728,15 +4722,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="M3">
-        <v>49</v>
-      </c>
-      <c r="N3">
         <v>49</v>
       </c>
     </row>
@@ -4772,17 +4763,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="M4">
         <v>49</v>
       </c>
-      <c r="N4">
-        <v>49</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -4816,15 +4804,12 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="M5">
-        <v>96</v>
-      </c>
-      <c r="N5">
         <v>96</v>
       </c>
     </row>
@@ -4860,15 +4845,12 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M6">
-        <v>16</v>
-      </c>
-      <c r="N6">
         <v>16</v>
       </c>
     </row>
@@ -4904,15 +4886,12 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M7">
-        <v>16</v>
-      </c>
-      <c r="N7">
         <v>16</v>
       </c>
     </row>
@@ -4948,15 +4927,12 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M8">
-        <v>16</v>
-      </c>
-      <c r="N8">
         <v>16</v>
       </c>
     </row>
@@ -4992,15 +4968,12 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M9">
-        <v>16</v>
-      </c>
-      <c r="N9">
         <v>16</v>
       </c>
     </row>
@@ -5036,15 +5009,12 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M10">
-        <v>16</v>
-      </c>
-      <c r="N10">
         <v>16</v>
       </c>
     </row>
@@ -5080,15 +5050,12 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M11">
-        <v>16</v>
-      </c>
-      <c r="N11">
         <v>16</v>
       </c>
     </row>
@@ -5124,15 +5091,12 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M12">
-        <v>16</v>
-      </c>
-      <c r="N12">
         <v>16</v>
       </c>
     </row>
@@ -5168,15 +5132,12 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M13">
-        <v>16</v>
-      </c>
-      <c r="N13">
         <v>16</v>
       </c>
     </row>
@@ -5212,15 +5173,12 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M14">
-        <v>16</v>
-      </c>
-      <c r="N14">
         <v>16</v>
       </c>
     </row>
@@ -5256,15 +5214,12 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M15">
-        <v>16</v>
-      </c>
-      <c r="N15">
         <v>16</v>
       </c>
     </row>
@@ -5300,15 +5255,12 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M16">
-        <v>16</v>
-      </c>
-      <c r="N16">
         <v>16</v>
       </c>
     </row>
@@ -5344,15 +5296,12 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M17">
-        <v>16</v>
-      </c>
-      <c r="N17">
         <v>16</v>
       </c>
     </row>
@@ -5388,15 +5337,12 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M18">
-        <v>16</v>
-      </c>
-      <c r="N18">
         <v>16</v>
       </c>
     </row>
@@ -5432,15 +5378,12 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M19">
-        <v>16</v>
-      </c>
-      <c r="N19">
         <v>16</v>
       </c>
     </row>
@@ -5476,15 +5419,12 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M20">
-        <v>16</v>
-      </c>
-      <c r="N20">
         <v>16</v>
       </c>
     </row>
@@ -5520,15 +5460,12 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M21">
-        <v>16</v>
-      </c>
-      <c r="N21">
         <v>16</v>
       </c>
     </row>
@@ -5564,15 +5501,12 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M22">
-        <v>16</v>
-      </c>
-      <c r="N22">
         <v>16</v>
       </c>
     </row>
@@ -5608,15 +5542,12 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M23">
-        <v>16</v>
-      </c>
-      <c r="N23">
         <v>16</v>
       </c>
     </row>
@@ -5652,15 +5583,12 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M24">
-        <v>16</v>
-      </c>
-      <c r="N24">
         <v>16</v>
       </c>
     </row>
@@ -5696,15 +5624,12 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M25">
-        <v>16</v>
-      </c>
-      <c r="N25">
         <v>16</v>
       </c>
     </row>
@@ -5740,15 +5665,12 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M26">
-        <v>16</v>
-      </c>
-      <c r="N26">
         <v>16</v>
       </c>
     </row>
@@ -5784,15 +5706,12 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M27">
-        <v>16</v>
-      </c>
-      <c r="N27">
         <v>16</v>
       </c>
     </row>
@@ -5828,15 +5747,12 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M28">
-        <v>16</v>
-      </c>
-      <c r="N28">
         <v>16</v>
       </c>
     </row>
@@ -5872,15 +5788,12 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M29">
-        <v>16</v>
-      </c>
-      <c r="N29">
         <v>16</v>
       </c>
     </row>
@@ -5916,15 +5829,12 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M30">
-        <v>16</v>
-      </c>
-      <c r="N30">
         <v>16</v>
       </c>
     </row>
@@ -5960,15 +5870,12 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M31">
-        <v>16</v>
-      </c>
-      <c r="N31">
         <v>16</v>
       </c>
     </row>
@@ -6004,15 +5911,12 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M32">
-        <v>16</v>
-      </c>
-      <c r="N32">
         <v>16</v>
       </c>
     </row>
@@ -6048,15 +5952,12 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M33">
-        <v>16</v>
-      </c>
-      <c r="N33">
         <v>16</v>
       </c>
     </row>
@@ -6092,15 +5993,12 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M34">
-        <v>16</v>
-      </c>
-      <c r="N34">
         <v>16</v>
       </c>
     </row>
@@ -6136,15 +6034,12 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M35">
-        <v>16</v>
-      </c>
-      <c r="N35">
         <v>16</v>
       </c>
     </row>
@@ -6180,15 +6075,12 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M36">
-        <v>16</v>
-      </c>
-      <c r="N36">
         <v>16</v>
       </c>
     </row>
@@ -6224,15 +6116,12 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M37">
-        <v>16</v>
-      </c>
-      <c r="N37">
         <v>16</v>
       </c>
     </row>
@@ -6268,15 +6157,12 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M38">
-        <v>16</v>
-      </c>
-      <c r="N38">
         <v>16</v>
       </c>
     </row>
@@ -6312,15 +6198,12 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M39">
-        <v>16</v>
-      </c>
-      <c r="N39">
         <v>16</v>
       </c>
     </row>
@@ -6356,15 +6239,12 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M40">
-        <v>16</v>
-      </c>
-      <c r="N40">
         <v>16</v>
       </c>
     </row>
@@ -6400,15 +6280,12 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M41">
-        <v>16</v>
-      </c>
-      <c r="N41">
         <v>16</v>
       </c>
     </row>
@@ -6444,15 +6321,12 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M42">
-        <v>16</v>
-      </c>
-      <c r="N42">
         <v>16</v>
       </c>
     </row>
@@ -6488,15 +6362,12 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M43">
-        <v>16</v>
-      </c>
-      <c r="N43">
         <v>16</v>
       </c>
     </row>
@@ -6532,15 +6403,12 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M44">
-        <v>16</v>
-      </c>
-      <c r="N44">
         <v>16</v>
       </c>
     </row>
@@ -6576,15 +6444,12 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L45">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M45">
-        <v>16</v>
-      </c>
-      <c r="N45">
         <v>16</v>
       </c>
     </row>
@@ -6620,15 +6485,12 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M46">
-        <v>16</v>
-      </c>
-      <c r="N46">
         <v>16</v>
       </c>
     </row>
@@ -6664,15 +6526,12 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M47">
-        <v>16</v>
-      </c>
-      <c r="N47">
         <v>16</v>
       </c>
     </row>
@@ -6708,15 +6567,12 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M48">
-        <v>16</v>
-      </c>
-      <c r="N48">
         <v>16</v>
       </c>
     </row>
@@ -6752,15 +6608,12 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M49">
-        <v>16</v>
-      </c>
-      <c r="N49">
         <v>16</v>
       </c>
     </row>
@@ -6796,15 +6649,12 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L50">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M50">
-        <v>16</v>
-      </c>
-      <c r="N50">
         <v>16</v>
       </c>
     </row>
@@ -6840,15 +6690,12 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M51">
-        <v>16</v>
-      </c>
-      <c r="N51">
         <v>16</v>
       </c>
     </row>
@@ -6884,15 +6731,12 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M52">
-        <v>16</v>
-      </c>
-      <c r="N52">
         <v>16</v>
       </c>
     </row>
@@ -6928,15 +6772,12 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L53">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M53">
-        <v>16</v>
-      </c>
-      <c r="N53">
         <v>16</v>
       </c>
     </row>
@@ -6972,15 +6813,12 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M54">
-        <v>16</v>
-      </c>
-      <c r="N54">
         <v>16</v>
       </c>
     </row>
@@ -7016,15 +6854,12 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M55">
-        <v>16</v>
-      </c>
-      <c r="N55">
         <v>16</v>
       </c>
     </row>
@@ -7060,15 +6895,12 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M56">
-        <v>16</v>
-      </c>
-      <c r="N56">
         <v>16</v>
       </c>
     </row>
@@ -7104,15 +6936,12 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M57">
-        <v>16</v>
-      </c>
-      <c r="N57">
         <v>16</v>
       </c>
     </row>
@@ -7148,15 +6977,12 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L58">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M58">
-        <v>16</v>
-      </c>
-      <c r="N58">
         <v>16</v>
       </c>
     </row>
@@ -7192,15 +7018,12 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L59">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M59">
-        <v>16</v>
-      </c>
-      <c r="N59">
         <v>16</v>
       </c>
     </row>
@@ -7236,15 +7059,12 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M60">
-        <v>16</v>
-      </c>
-      <c r="N60">
         <v>16</v>
       </c>
     </row>
@@ -7280,15 +7100,12 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M61">
-        <v>16</v>
-      </c>
-      <c r="N61">
         <v>16</v>
       </c>
     </row>
@@ -7324,15 +7141,12 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L62">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M62">
-        <v>16</v>
-      </c>
-      <c r="N62">
         <v>16</v>
       </c>
     </row>
@@ -7368,15 +7182,12 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L63">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M63">
-        <v>16</v>
-      </c>
-      <c r="N63">
         <v>16</v>
       </c>
     </row>
@@ -7412,15 +7223,12 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L64">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M64">
-        <v>16</v>
-      </c>
-      <c r="N64">
         <v>16</v>
       </c>
     </row>
@@ -7456,15 +7264,12 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L65">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M65">
-        <v>16</v>
-      </c>
-      <c r="N65">
         <v>16</v>
       </c>
     </row>
@@ -7500,15 +7305,12 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M66">
-        <v>16</v>
-      </c>
-      <c r="N66">
         <v>16</v>
       </c>
     </row>
@@ -7544,15 +7346,12 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M67">
-        <v>16</v>
-      </c>
-      <c r="N67">
         <v>16</v>
       </c>
     </row>
@@ -7588,15 +7387,12 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L68">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M68">
-        <v>16</v>
-      </c>
-      <c r="N68">
         <v>16</v>
       </c>
     </row>
@@ -7632,15 +7428,12 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M69">
-        <v>16</v>
-      </c>
-      <c r="N69">
         <v>16</v>
       </c>
     </row>
@@ -7676,15 +7469,12 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M70">
-        <v>16</v>
-      </c>
-      <c r="N70">
         <v>16</v>
       </c>
     </row>
@@ -7720,15 +7510,12 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M71">
-        <v>16</v>
-      </c>
-      <c r="N71">
         <v>16</v>
       </c>
     </row>
@@ -7764,15 +7551,12 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M72">
-        <v>16</v>
-      </c>
-      <c r="N72">
         <v>16</v>
       </c>
     </row>
@@ -7808,15 +7592,12 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M73">
-        <v>16</v>
-      </c>
-      <c r="N73">
         <v>16</v>
       </c>
     </row>
@@ -7852,15 +7633,12 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M74">
-        <v>16</v>
-      </c>
-      <c r="N74">
         <v>16</v>
       </c>
     </row>
@@ -7896,15 +7674,12 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M75">
-        <v>16</v>
-      </c>
-      <c r="N75">
         <v>16</v>
       </c>
     </row>
@@ -7940,15 +7715,12 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M76">
-        <v>16</v>
-      </c>
-      <c r="N76">
         <v>16</v>
       </c>
     </row>
@@ -7984,15 +7756,12 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L77">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M77">
-        <v>16</v>
-      </c>
-      <c r="N77">
         <v>16</v>
       </c>
     </row>
@@ -8028,15 +7797,12 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L78">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M78">
-        <v>16</v>
-      </c>
-      <c r="N78">
         <v>16</v>
       </c>
     </row>
@@ -8072,15 +7838,12 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M79">
-        <v>16</v>
-      </c>
-      <c r="N79">
         <v>16</v>
       </c>
     </row>
@@ -8116,15 +7879,12 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M80">
-        <v>16</v>
-      </c>
-      <c r="N80">
         <v>16</v>
       </c>
     </row>
@@ -8160,15 +7920,12 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M81">
-        <v>16</v>
-      </c>
-      <c r="N81">
         <v>16</v>
       </c>
     </row>
@@ -8204,15 +7961,12 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L82">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M82">
-        <v>16</v>
-      </c>
-      <c r="N82">
         <v>16</v>
       </c>
     </row>
@@ -8248,15 +8002,12 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L83">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M83">
-        <v>16</v>
-      </c>
-      <c r="N83">
         <v>16</v>
       </c>
     </row>
@@ -8292,15 +8043,12 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L84">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M84">
-        <v>16</v>
-      </c>
-      <c r="N84">
         <v>16</v>
       </c>
     </row>
@@ -8336,15 +8084,12 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L85">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M85">
-        <v>16</v>
-      </c>
-      <c r="N85">
         <v>16</v>
       </c>
     </row>
@@ -8380,15 +8125,12 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L86">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M86">
-        <v>16</v>
-      </c>
-      <c r="N86">
         <v>16</v>
       </c>
     </row>
@@ -8424,15 +8166,12 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L87">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M87">
-        <v>16</v>
-      </c>
-      <c r="N87">
         <v>16</v>
       </c>
     </row>
@@ -8468,15 +8207,12 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L88">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M88">
-        <v>16</v>
-      </c>
-      <c r="N88">
         <v>16</v>
       </c>
     </row>
@@ -8512,15 +8248,12 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L89">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M89">
-        <v>16</v>
-      </c>
-      <c r="N89">
         <v>16</v>
       </c>
     </row>
@@ -8556,15 +8289,12 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L90">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M90">
-        <v>16</v>
-      </c>
-      <c r="N90">
         <v>16</v>
       </c>
     </row>
@@ -8600,15 +8330,12 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L91">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M91">
-        <v>16</v>
-      </c>
-      <c r="N91">
         <v>16</v>
       </c>
     </row>
@@ -8644,15 +8371,12 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L92">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M92">
-        <v>16</v>
-      </c>
-      <c r="N92">
         <v>16</v>
       </c>
     </row>
@@ -8688,15 +8412,12 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L93">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M93">
-        <v>16</v>
-      </c>
-      <c r="N93">
         <v>16</v>
       </c>
     </row>
@@ -8732,15 +8453,12 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L94">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M94">
-        <v>16</v>
-      </c>
-      <c r="N94">
         <v>16</v>
       </c>
     </row>
@@ -8776,15 +8494,12 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L95">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M95">
-        <v>16</v>
-      </c>
-      <c r="N95">
         <v>16</v>
       </c>
     </row>
@@ -8820,15 +8535,12 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L96">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M96">
-        <v>16</v>
-      </c>
-      <c r="N96">
         <v>16</v>
       </c>
     </row>
@@ -8864,15 +8576,12 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L97">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M97">
-        <v>16</v>
-      </c>
-      <c r="N97">
         <v>16</v>
       </c>
     </row>
@@ -8908,15 +8617,12 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L98">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M98">
-        <v>16</v>
-      </c>
-      <c r="N98">
         <v>16</v>
       </c>
     </row>
@@ -8952,15 +8658,12 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L99">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M99">
-        <v>16</v>
-      </c>
-      <c r="N99">
         <v>16</v>
       </c>
     </row>
@@ -8996,15 +8699,12 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L100">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M100">
-        <v>16</v>
-      </c>
-      <c r="N100">
         <v>16</v>
       </c>
     </row>
@@ -9040,15 +8740,12 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L101">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M101">
-        <v>16</v>
-      </c>
-      <c r="N101">
         <v>16</v>
       </c>
     </row>
@@ -9084,15 +8781,12 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L102">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M102">
-        <v>16</v>
-      </c>
-      <c r="N102">
         <v>16</v>
       </c>
     </row>
@@ -9128,15 +8822,12 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L103">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M103">
-        <v>16</v>
-      </c>
-      <c r="N103">
         <v>16</v>
       </c>
     </row>
@@ -9172,15 +8863,12 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L104">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M104">
-        <v>16</v>
-      </c>
-      <c r="N104">
         <v>16</v>
       </c>
     </row>
@@ -9216,15 +8904,12 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L105">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M105">
-        <v>16</v>
-      </c>
-      <c r="N105">
         <v>16</v>
       </c>
     </row>
@@ -9260,15 +8945,12 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L106">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M106">
-        <v>16</v>
-      </c>
-      <c r="N106">
         <v>16</v>
       </c>
     </row>
@@ -9304,15 +8986,12 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L107">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M107">
-        <v>16</v>
-      </c>
-      <c r="N107">
         <v>16</v>
       </c>
     </row>
@@ -9348,15 +9027,12 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L108">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M108">
-        <v>16</v>
-      </c>
-      <c r="N108">
         <v>16</v>
       </c>
     </row>
@@ -9392,15 +9068,12 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L109">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M109">
-        <v>16</v>
-      </c>
-      <c r="N109">
         <v>16</v>
       </c>
     </row>
@@ -9436,15 +9109,12 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L110">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M110">
-        <v>16</v>
-      </c>
-      <c r="N110">
         <v>16</v>
       </c>
     </row>
@@ -9480,15 +9150,12 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L111">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M111">
-        <v>16</v>
-      </c>
-      <c r="N111">
         <v>16</v>
       </c>
     </row>
@@ -9524,15 +9191,12 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L112">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M112">
-        <v>16</v>
-      </c>
-      <c r="N112">
         <v>16</v>
       </c>
     </row>
@@ -9568,15 +9232,12 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L113">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M113">
-        <v>16</v>
-      </c>
-      <c r="N113">
         <v>16</v>
       </c>
     </row>
@@ -9612,15 +9273,12 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L114">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M114">
-        <v>16</v>
-      </c>
-      <c r="N114">
         <v>16</v>
       </c>
     </row>
@@ -9656,15 +9314,12 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L115">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M115">
-        <v>16</v>
-      </c>
-      <c r="N115">
         <v>16</v>
       </c>
     </row>
@@ -9700,15 +9355,12 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L116">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M116">
-        <v>16</v>
-      </c>
-      <c r="N116">
         <v>16</v>
       </c>
     </row>
@@ -9744,15 +9396,12 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L117">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M117">
-        <v>16</v>
-      </c>
-      <c r="N117">
         <v>16</v>
       </c>
     </row>
@@ -9788,15 +9437,12 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L118">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M118">
-        <v>16</v>
-      </c>
-      <c r="N118">
         <v>16</v>
       </c>
     </row>
@@ -9832,15 +9478,12 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L119">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M119">
-        <v>16</v>
-      </c>
-      <c r="N119">
         <v>16</v>
       </c>
     </row>
@@ -9876,15 +9519,12 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L120">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M120">
-        <v>16</v>
-      </c>
-      <c r="N120">
         <v>16</v>
       </c>
     </row>
@@ -9920,15 +9560,12 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L121">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M121">
-        <v>16</v>
-      </c>
-      <c r="N121">
         <v>16</v>
       </c>
     </row>
@@ -9964,15 +9601,12 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L122">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M122">
-        <v>16</v>
-      </c>
-      <c r="N122">
         <v>16</v>
       </c>
     </row>
@@ -10008,15 +9642,12 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L123">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M123">
-        <v>16</v>
-      </c>
-      <c r="N123">
         <v>16</v>
       </c>
     </row>
@@ -10052,15 +9683,12 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L124">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M124">
-        <v>16</v>
-      </c>
-      <c r="N124">
         <v>16</v>
       </c>
     </row>
@@ -10096,15 +9724,12 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L125">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M125">
-        <v>16</v>
-      </c>
-      <c r="N125">
         <v>16</v>
       </c>
     </row>
@@ -10140,15 +9765,12 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L126">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M126">
-        <v>16</v>
-      </c>
-      <c r="N126">
         <v>16</v>
       </c>
     </row>
@@ -10184,15 +9806,12 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L127">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M127">
-        <v>16</v>
-      </c>
-      <c r="N127">
         <v>16</v>
       </c>
     </row>
@@ -10228,15 +9847,12 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L128">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M128">
-        <v>16</v>
-      </c>
-      <c r="N128">
         <v>16</v>
       </c>
     </row>
@@ -10272,15 +9888,12 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L129">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M129">
-        <v>16</v>
-      </c>
-      <c r="N129">
         <v>16</v>
       </c>
     </row>
@@ -10316,15 +9929,12 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L130">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M130">
-        <v>16</v>
-      </c>
-      <c r="N130">
         <v>16</v>
       </c>
     </row>
@@ -10360,15 +9970,12 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L131">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M131">
-        <v>16</v>
-      </c>
-      <c r="N131">
         <v>16</v>
       </c>
     </row>
@@ -10404,15 +10011,12 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L132">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M132">
-        <v>16</v>
-      </c>
-      <c r="N132">
         <v>16</v>
       </c>
     </row>
@@ -10448,15 +10052,12 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L133">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M133">
-        <v>16</v>
-      </c>
-      <c r="N133">
         <v>16</v>
       </c>
     </row>
@@ -10492,15 +10093,12 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L134">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M134">
-        <v>16</v>
-      </c>
-      <c r="N134">
         <v>16</v>
       </c>
     </row>
@@ -10536,15 +10134,12 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L135">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M135">
-        <v>16</v>
-      </c>
-      <c r="N135">
         <v>16</v>
       </c>
     </row>
@@ -10580,15 +10175,12 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L136">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M136">
-        <v>16</v>
-      </c>
-      <c r="N136">
         <v>16</v>
       </c>
     </row>
@@ -10624,15 +10216,12 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L137">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M137">
-        <v>16</v>
-      </c>
-      <c r="N137">
         <v>16</v>
       </c>
     </row>
@@ -10668,15 +10257,12 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L138">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M138">
-        <v>16</v>
-      </c>
-      <c r="N138">
         <v>16</v>
       </c>
     </row>
@@ -10712,15 +10298,12 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L139">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M139">
-        <v>16</v>
-      </c>
-      <c r="N139">
         <v>16</v>
       </c>
     </row>
@@ -10756,15 +10339,12 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L140">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M140">
-        <v>16</v>
-      </c>
-      <c r="N140">
         <v>16</v>
       </c>
     </row>
@@ -10800,15 +10380,12 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L141">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M141">
-        <v>16</v>
-      </c>
-      <c r="N141">
         <v>16</v>
       </c>
     </row>
@@ -10844,15 +10421,12 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L142">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M142">
-        <v>16</v>
-      </c>
-      <c r="N142">
         <v>16</v>
       </c>
     </row>
@@ -10888,15 +10462,12 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L143">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M143">
-        <v>16</v>
-      </c>
-      <c r="N143">
         <v>16</v>
       </c>
     </row>
@@ -10932,15 +10503,12 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L144">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M144">
-        <v>16</v>
-      </c>
-      <c r="N144">
         <v>16</v>
       </c>
     </row>
@@ -10976,15 +10544,12 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L145">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M145">
-        <v>16</v>
-      </c>
-      <c r="N145">
         <v>16</v>
       </c>
     </row>
@@ -11020,15 +10585,12 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L146">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M146">
-        <v>16</v>
-      </c>
-      <c r="N146">
         <v>16</v>
       </c>
     </row>
@@ -11064,15 +10626,12 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L147">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M147">
-        <v>16</v>
-      </c>
-      <c r="N147">
         <v>16</v>
       </c>
     </row>
@@ -11108,15 +10667,12 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L148">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M148">
-        <v>16</v>
-      </c>
-      <c r="N148">
         <v>16</v>
       </c>
     </row>
@@ -11152,15 +10708,12 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L149">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M149">
-        <v>16</v>
-      </c>
-      <c r="N149">
         <v>16</v>
       </c>
     </row>
@@ -11196,15 +10749,12 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L150">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M150">
-        <v>16</v>
-      </c>
-      <c r="N150">
         <v>16</v>
       </c>
     </row>
@@ -11240,15 +10790,12 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L151">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M151">
-        <v>16</v>
-      </c>
-      <c r="N151">
         <v>16</v>
       </c>
     </row>
@@ -11284,15 +10831,12 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L152">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M152">
-        <v>16</v>
-      </c>
-      <c r="N152">
         <v>16</v>
       </c>
     </row>
@@ -11328,15 +10872,12 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L153">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M153">
-        <v>16</v>
-      </c>
-      <c r="N153">
         <v>16</v>
       </c>
     </row>
@@ -11372,15 +10913,12 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L154">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M154">
-        <v>16</v>
-      </c>
-      <c r="N154">
         <v>16</v>
       </c>
     </row>
@@ -11416,15 +10954,12 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L155">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M155">
-        <v>16</v>
-      </c>
-      <c r="N155">
         <v>16</v>
       </c>
     </row>
@@ -11460,15 +10995,12 @@
         <v>0</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L156">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M156">
-        <v>16</v>
-      </c>
-      <c r="N156">
         <v>16</v>
       </c>
     </row>
@@ -11504,15 +11036,12 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L157">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M157">
-        <v>16</v>
-      </c>
-      <c r="N157">
         <v>16</v>
       </c>
     </row>
@@ -11548,15 +11077,12 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L158">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M158">
-        <v>16</v>
-      </c>
-      <c r="N158">
         <v>16</v>
       </c>
     </row>
@@ -11592,15 +11118,12 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L159">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M159">
-        <v>16</v>
-      </c>
-      <c r="N159">
         <v>16</v>
       </c>
     </row>
@@ -11636,15 +11159,12 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L160">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M160">
-        <v>16</v>
-      </c>
-      <c r="N160">
         <v>16</v>
       </c>
     </row>
@@ -11680,15 +11200,12 @@
         <v>0</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L161">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M161">
-        <v>16</v>
-      </c>
-      <c r="N161">
         <v>16</v>
       </c>
     </row>
@@ -11724,15 +11241,12 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L162">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M162">
-        <v>16</v>
-      </c>
-      <c r="N162">
         <v>16</v>
       </c>
     </row>
@@ -11768,15 +11282,12 @@
         <v>0</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L163">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M163">
-        <v>16</v>
-      </c>
-      <c r="N163">
         <v>16</v>
       </c>
     </row>
@@ -11812,15 +11323,12 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L164">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M164">
-        <v>16</v>
-      </c>
-      <c r="N164">
         <v>16</v>
       </c>
     </row>
@@ -11856,15 +11364,12 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L165">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M165">
-        <v>16</v>
-      </c>
-      <c r="N165">
         <v>16</v>
       </c>
     </row>
@@ -11900,15 +11405,12 @@
         <v>0</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L166">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M166">
-        <v>16</v>
-      </c>
-      <c r="N166">
         <v>16</v>
       </c>
     </row>
@@ -11944,15 +11446,12 @@
         <v>0</v>
       </c>
       <c r="K167">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L167">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M167">
-        <v>16</v>
-      </c>
-      <c r="N167">
         <v>16</v>
       </c>
     </row>
@@ -11988,15 +11487,12 @@
         <v>0</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L168">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M168">
-        <v>16</v>
-      </c>
-      <c r="N168">
         <v>16</v>
       </c>
     </row>
@@ -12032,15 +11528,12 @@
         <v>0</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L169">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M169">
-        <v>16</v>
-      </c>
-      <c r="N169">
         <v>16</v>
       </c>
     </row>
@@ -12076,15 +11569,12 @@
         <v>0</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L170">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M170">
-        <v>16</v>
-      </c>
-      <c r="N170">
         <v>16</v>
       </c>
     </row>
@@ -12120,15 +11610,12 @@
         <v>0</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L171">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M171">
-        <v>16</v>
-      </c>
-      <c r="N171">
         <v>16</v>
       </c>
     </row>
@@ -12164,15 +11651,12 @@
         <v>0</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L172">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M172">
-        <v>16</v>
-      </c>
-      <c r="N172">
         <v>16</v>
       </c>
     </row>
@@ -12208,15 +11692,12 @@
         <v>0</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L173">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M173">
-        <v>16</v>
-      </c>
-      <c r="N173">
         <v>16</v>
       </c>
     </row>
@@ -12252,15 +11733,12 @@
         <v>0</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L174">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M174">
-        <v>16</v>
-      </c>
-      <c r="N174">
         <v>16</v>
       </c>
     </row>
@@ -12296,15 +11774,12 @@
         <v>0</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L175">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M175">
-        <v>16</v>
-      </c>
-      <c r="N175">
         <v>16</v>
       </c>
     </row>
@@ -12340,15 +11815,12 @@
         <v>0</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L176">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M176">
-        <v>16</v>
-      </c>
-      <c r="N176">
         <v>16</v>
       </c>
     </row>
@@ -12384,15 +11856,12 @@
         <v>0</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L177">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M177">
-        <v>16</v>
-      </c>
-      <c r="N177">
         <v>16</v>
       </c>
     </row>
@@ -12428,15 +11897,12 @@
         <v>0</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L178">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M178">
-        <v>16</v>
-      </c>
-      <c r="N178">
         <v>16</v>
       </c>
     </row>
@@ -12472,15 +11938,12 @@
         <v>0</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L179">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M179">
-        <v>16</v>
-      </c>
-      <c r="N179">
         <v>16</v>
       </c>
     </row>
@@ -12516,15 +11979,12 @@
         <v>0</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L180">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M180">
-        <v>16</v>
-      </c>
-      <c r="N180">
         <v>16</v>
       </c>
     </row>
@@ -12560,15 +12020,12 @@
         <v>0</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L181">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M181">
-        <v>16</v>
-      </c>
-      <c r="N181">
         <v>16</v>
       </c>
     </row>
@@ -12604,15 +12061,12 @@
         <v>0</v>
       </c>
       <c r="K182">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L182">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M182">
-        <v>16</v>
-      </c>
-      <c r="N182">
         <v>16</v>
       </c>
     </row>
@@ -12648,15 +12102,12 @@
         <v>0</v>
       </c>
       <c r="K183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L183">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M183">
-        <v>16</v>
-      </c>
-      <c r="N183">
         <v>16</v>
       </c>
     </row>
@@ -12692,15 +12143,12 @@
         <v>0</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L184">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M184">
-        <v>16</v>
-      </c>
-      <c r="N184">
         <v>16</v>
       </c>
     </row>
@@ -12736,15 +12184,12 @@
         <v>0</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L185">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M185">
-        <v>16</v>
-      </c>
-      <c r="N185">
         <v>16</v>
       </c>
     </row>
@@ -12780,15 +12225,12 @@
         <v>0</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L186">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M186">
-        <v>16</v>
-      </c>
-      <c r="N186">
         <v>16</v>
       </c>
     </row>
@@ -12824,15 +12266,12 @@
         <v>0</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L187">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M187">
-        <v>16</v>
-      </c>
-      <c r="N187">
         <v>16</v>
       </c>
     </row>
@@ -12868,15 +12307,12 @@
         <v>0</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L188">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M188">
-        <v>16</v>
-      </c>
-      <c r="N188">
         <v>16</v>
       </c>
     </row>
@@ -12912,15 +12348,12 @@
         <v>0</v>
       </c>
       <c r="K189">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L189">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M189">
-        <v>16</v>
-      </c>
-      <c r="N189">
         <v>16</v>
       </c>
     </row>
@@ -12956,15 +12389,12 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L190">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M190">
-        <v>16</v>
-      </c>
-      <c r="N190">
         <v>16</v>
       </c>
     </row>
@@ -13000,15 +12430,12 @@
         <v>0</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L191">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M191">
-        <v>16</v>
-      </c>
-      <c r="N191">
         <v>16</v>
       </c>
     </row>
@@ -13044,15 +12471,12 @@
         <v>0</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L192">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M192">
-        <v>16</v>
-      </c>
-      <c r="N192">
         <v>16</v>
       </c>
     </row>
@@ -13088,15 +12512,12 @@
         <v>0</v>
       </c>
       <c r="K193">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L193">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M193">
-        <v>16</v>
-      </c>
-      <c r="N193">
         <v>16</v>
       </c>
     </row>
@@ -13132,15 +12553,12 @@
         <v>0</v>
       </c>
       <c r="K194">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L194">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M194">
-        <v>16</v>
-      </c>
-      <c r="N194">
         <v>16</v>
       </c>
     </row>
@@ -13176,15 +12594,12 @@
         <v>0</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L195">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M195">
-        <v>16</v>
-      </c>
-      <c r="N195">
         <v>16</v>
       </c>
     </row>
@@ -13220,15 +12635,12 @@
         <v>0</v>
       </c>
       <c r="K196">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L196">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M196">
-        <v>16</v>
-      </c>
-      <c r="N196">
         <v>16</v>
       </c>
     </row>
@@ -13264,15 +12676,12 @@
         <v>0</v>
       </c>
       <c r="K197">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L197">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M197">
-        <v>16</v>
-      </c>
-      <c r="N197">
         <v>16</v>
       </c>
     </row>
@@ -13308,15 +12717,12 @@
         <v>0</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L198">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M198">
-        <v>16</v>
-      </c>
-      <c r="N198">
         <v>16</v>
       </c>
     </row>
@@ -13352,15 +12758,12 @@
         <v>0</v>
       </c>
       <c r="K199">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L199">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M199">
-        <v>16</v>
-      </c>
-      <c r="N199">
         <v>16</v>
       </c>
     </row>
@@ -13396,21 +12799,18 @@
         <v>0</v>
       </c>
       <c r="K200">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L200">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M200">
-        <v>16</v>
-      </c>
-      <c r="N200">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M200"/>
   </ignoredErrors>
 </worksheet>
 </file>